--- a/data/output/sim_gridrnd/REL2/group_500_20/results/REL2_G4_results_summary.xlsx
+++ b/data/output/sim_gridrnd/REL2/group_500_20/results/REL2_G4_results_summary.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Results" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB23"/>
+  <dimension ref="A1:CM23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,24 +436,24 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>mu</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>sigma</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>jnd</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>pse</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>jnd</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>sigma</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>mu</t>
-        </is>
-      </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
           <t>n_trials</t>
@@ -466,860 +466,981 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>lat_entropy_100</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_120</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_140</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_160</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_180</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_200</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_40</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_60</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_80</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
           <t>model</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>pse_40</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>jnd_40</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>pse_60</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>jnd_60</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>pse_80</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>jnd_80</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>pse_100</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>jnd_100</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>pse_120</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>jnd_120</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>pse_140</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>jnd_140</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>pse_160</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>jnd_160</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>pse_180</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>jnd_180</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>pse_200</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>jnd_200</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_40</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_60</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_80</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_100</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_120</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_140</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_160</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_180</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_200</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_40</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_60</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_80</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_100</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_120</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_140</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_160</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_180</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_200</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_40</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_60</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_80</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_100</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_120</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_140</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_160</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_180</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_200</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_40</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_60</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_80</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_100</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_120</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_140</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_160</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_180</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_200</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_40</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_60</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_80</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_100</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_120</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_140</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_160</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_180</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_200</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_40</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_60</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_80</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_100</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_120</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_140</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_160</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_180</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CK1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_200</t>
+        </is>
+      </c>
+      <c r="CL1" s="1" t="inlineStr">
+        <is>
+          <t>pse_est</t>
+        </is>
+      </c>
+      <c r="CM1" s="1" t="inlineStr">
+        <is>
+          <t>jnd_est</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>S02_G4_498_19_REL2</t>
+          <t>S01_G4_499_22_REL2</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C2" t="n">
-        <v>19</v>
+        <v>32.61675315048184</v>
       </c>
       <c r="D2" t="n">
-        <v>28.16901408450704</v>
+        <v>22</v>
       </c>
       <c r="E2" t="n">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="F2" t="n">
         <v>200</v>
       </c>
       <c r="G2" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="H2" t="inlineStr">
+        <v>81.5</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="J2" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="K2" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="L2" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="M2" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="N2" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="O2" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="P2" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="Q2" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I2" t="n">
-        <v>500.8148314973537</v>
-      </c>
-      <c r="J2" t="n">
-        <v>6.006432751887999</v>
-      </c>
-      <c r="K2" t="n">
-        <v>500.2190526266183</v>
-      </c>
-      <c r="L2" t="n">
-        <v>9.268533198925939</v>
-      </c>
-      <c r="M2" t="n">
-        <v>497.6631674120523</v>
-      </c>
-      <c r="N2" t="n">
-        <v>13.02211475696609</v>
-      </c>
-      <c r="O2" t="n">
-        <v>496.7186541158488</v>
-      </c>
-      <c r="P2" t="n">
-        <v>14.58975023717218</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>494.7633157194997</v>
-      </c>
       <c r="R2" t="n">
-        <v>16.26548033769962</v>
+        <v>505.25</v>
       </c>
       <c r="S2" t="n">
-        <v>495.5473899177461</v>
+        <v>18.43</v>
       </c>
       <c r="T2" t="n">
-        <v>18.7868915267707</v>
+        <v>496.32</v>
       </c>
       <c r="U2" t="n">
-        <v>495.6116829177762</v>
+        <v>20.89</v>
       </c>
       <c r="V2" t="n">
-        <v>17.97735287597303</v>
+        <v>494.65</v>
       </c>
       <c r="W2" t="n">
-        <v>496.7080551131627</v>
+        <v>22.65</v>
       </c>
       <c r="X2" t="n">
-        <v>19.47201813129838</v>
+        <v>500.72</v>
       </c>
       <c r="Y2" t="n">
-        <v>496.0354769269234</v>
+        <v>22.98</v>
       </c>
       <c r="Z2" t="n">
-        <v>18.66048963234457</v>
+        <v>500.48</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>21.42</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>499.97</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>21.56</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>497.3</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>23.06</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>497.36</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>22.74</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>499.19</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>22.9</v>
       </c>
       <c r="AJ2" t="n">
-        <v>498.925</v>
+        <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>498.9666666666666</v>
+        <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>499.4875</v>
+        <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>498.14</v>
+        <v>0</v>
       </c>
       <c r="AN2" t="n">
-        <v>497.3</v>
+        <v>0</v>
       </c>
       <c r="AO2" t="n">
-        <v>496.7</v>
+        <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>496.43125</v>
+        <v>0</v>
       </c>
       <c r="AQ2" t="n">
-        <v>496.5</v>
+        <v>0</v>
       </c>
       <c r="AR2" t="n">
-        <v>497.23</v>
+        <v>0</v>
       </c>
       <c r="AS2" t="n">
-        <v>66.53058976891758</v>
+        <v>503.425</v>
       </c>
       <c r="AT2" t="n">
-        <v>54.88866509176149</v>
+        <v>502.7</v>
       </c>
       <c r="AU2" t="n">
-        <v>48.02238898420194</v>
+        <v>500.925</v>
       </c>
       <c r="AV2" t="n">
-        <v>43.97613443676013</v>
+        <v>500.28</v>
       </c>
       <c r="AW2" t="n">
-        <v>41.03059833831333</v>
+        <v>499.9916666666667</v>
       </c>
       <c r="AX2" t="n">
-        <v>39.12520196205291</v>
+        <v>499.4428571428571</v>
       </c>
       <c r="AY2" t="n">
-        <v>37.73105847226526</v>
+        <v>498.2125</v>
       </c>
       <c r="AZ2" t="n">
-        <v>37.00322808741001</v>
+        <v>497.1222222222222</v>
       </c>
       <c r="BA2" t="n">
-        <v>36.18932301107607</v>
+        <v>497.465</v>
       </c>
       <c r="BB2" t="n">
-        <v>320</v>
+        <v>67.42139404521387</v>
       </c>
       <c r="BC2" t="n">
-        <v>320</v>
+        <v>56.60397512542737</v>
       </c>
       <c r="BD2" t="n">
-        <v>320</v>
+        <v>50.83988960452216</v>
       </c>
       <c r="BE2" t="n">
-        <v>320</v>
+        <v>47.11519500118831</v>
       </c>
       <c r="BF2" t="n">
-        <v>320</v>
+        <v>44.29079961521981</v>
       </c>
       <c r="BG2" t="n">
-        <v>320</v>
+        <v>42.32616067576907</v>
       </c>
       <c r="BH2" t="n">
-        <v>320</v>
+        <v>41.41246604284753</v>
       </c>
       <c r="BI2" t="n">
-        <v>320</v>
+        <v>40.74714107974742</v>
       </c>
       <c r="BJ2" t="n">
-        <v>320</v>
+        <v>39.29056852477449</v>
       </c>
       <c r="BK2" t="n">
-        <v>669</v>
+        <v>340</v>
       </c>
       <c r="BL2" t="n">
-        <v>669</v>
+        <v>340</v>
       </c>
       <c r="BM2" t="n">
-        <v>669</v>
+        <v>340</v>
       </c>
       <c r="BN2" t="n">
-        <v>669</v>
+        <v>340</v>
       </c>
       <c r="BO2" t="n">
-        <v>669</v>
+        <v>340</v>
       </c>
       <c r="BP2" t="n">
-        <v>669</v>
+        <v>340</v>
       </c>
       <c r="BQ2" t="n">
-        <v>669</v>
+        <v>340</v>
       </c>
       <c r="BR2" t="n">
-        <v>669</v>
+        <v>340</v>
       </c>
       <c r="BS2" t="n">
-        <v>669</v>
+        <v>340</v>
       </c>
       <c r="BT2" t="n">
-        <v>0</v>
+        <v>669</v>
       </c>
       <c r="BU2" t="n">
-        <v>0</v>
+        <v>669</v>
       </c>
       <c r="BV2" t="n">
-        <v>0</v>
+        <v>669</v>
       </c>
       <c r="BW2" t="n">
-        <v>0</v>
+        <v>669</v>
       </c>
       <c r="BX2" t="n">
-        <v>0</v>
+        <v>669</v>
       </c>
       <c r="BY2" t="n">
-        <v>0</v>
+        <v>669</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0.7391304347826086</v>
+        <v>669</v>
       </c>
       <c r="CA2" t="n">
-        <v>0.7735849056603774</v>
+        <v>669</v>
       </c>
       <c r="CB2" t="n">
-        <v>0.7457627118644068</v>
+        <v>669</v>
+      </c>
+      <c r="CC2" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD2" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="CF2" t="n">
+        <v>0.8214285714285714</v>
+      </c>
+      <c r="CG2" t="n">
+        <v>0.7567567567567568</v>
+      </c>
+      <c r="CH2" t="n">
+        <v>0.7173913043478261</v>
+      </c>
+      <c r="CI2" t="n">
+        <v>0.0196078431372549</v>
+      </c>
+      <c r="CJ2" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="CK2" t="n">
+        <v>0.6964285714285714</v>
+      </c>
+      <c r="CL2" t="n">
+        <v>499.19</v>
+      </c>
+      <c r="CM2" t="n">
+        <v>22.9</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S01_G4_499_22_REL2</t>
+          <t>S02_G4_498_19_REL2</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C3" t="n">
-        <v>22</v>
+        <v>28.16901408450704</v>
       </c>
       <c r="D3" t="n">
-        <v>32.61675315048184</v>
+        <v>19</v>
       </c>
       <c r="E3" t="n">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="F3" t="n">
         <v>200</v>
       </c>
       <c r="G3" t="n">
-        <v>0.495</v>
-      </c>
-      <c r="H3" t="inlineStr">
+        <v>80</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="N3" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="Q3" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I3" t="n">
-        <v>505.248406439535</v>
-      </c>
-      <c r="J3" t="n">
-        <v>18.42685668645117</v>
-      </c>
-      <c r="K3" t="n">
-        <v>496.3219394931756</v>
-      </c>
-      <c r="L3" t="n">
-        <v>20.88543583442373</v>
-      </c>
-      <c r="M3" t="n">
-        <v>494.6495850262301</v>
-      </c>
-      <c r="N3" t="n">
-        <v>22.65321006208212</v>
-      </c>
-      <c r="O3" t="n">
-        <v>500.7205038215657</v>
-      </c>
-      <c r="P3" t="n">
-        <v>22.98023367722132</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>500.4757727291172</v>
-      </c>
       <c r="R3" t="n">
-        <v>21.41904588847693</v>
+        <v>500.81</v>
       </c>
       <c r="S3" t="n">
-        <v>499.9719945738026</v>
+        <v>6.01</v>
       </c>
       <c r="T3" t="n">
-        <v>21.56093929191801</v>
+        <v>500.22</v>
       </c>
       <c r="U3" t="n">
-        <v>497.3009756438051</v>
+        <v>9.27</v>
       </c>
       <c r="V3" t="n">
-        <v>23.05786002195033</v>
+        <v>497.66</v>
       </c>
       <c r="W3" t="n">
-        <v>497.3642321347228</v>
+        <v>13.02</v>
       </c>
       <c r="X3" t="n">
-        <v>22.73903053794824</v>
+        <v>496.72</v>
       </c>
       <c r="Y3" t="n">
-        <v>499.1860126652834</v>
+        <v>14.59</v>
       </c>
       <c r="Z3" t="n">
-        <v>22.90276014619208</v>
+        <v>494.76</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>16.27</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>495.55</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>18.79</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>495.61</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>17.98</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>496.71</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>19.47</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>496.04</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>18.66</v>
       </c>
       <c r="AJ3" t="n">
-        <v>503.425</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>502.7</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>500.925</v>
+        <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>500.28</v>
+        <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>499.9916666666667</v>
+        <v>0</v>
       </c>
       <c r="AO3" t="n">
-        <v>499.4428571428571</v>
+        <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>498.2125</v>
+        <v>0</v>
       </c>
       <c r="AQ3" t="n">
-        <v>497.1222222222222</v>
+        <v>0</v>
       </c>
       <c r="AR3" t="n">
-        <v>497.465</v>
+        <v>0</v>
       </c>
       <c r="AS3" t="n">
-        <v>67.42139404521387</v>
+        <v>498.925</v>
       </c>
       <c r="AT3" t="n">
-        <v>56.60397512542737</v>
+        <v>498.9666666666666</v>
       </c>
       <c r="AU3" t="n">
-        <v>50.83988960452216</v>
+        <v>499.4875</v>
       </c>
       <c r="AV3" t="n">
-        <v>47.11519500118831</v>
+        <v>498.14</v>
       </c>
       <c r="AW3" t="n">
-        <v>44.29079961521981</v>
+        <v>497.3</v>
       </c>
       <c r="AX3" t="n">
-        <v>42.32616067576907</v>
+        <v>496.7</v>
       </c>
       <c r="AY3" t="n">
-        <v>41.41246604284753</v>
+        <v>496.43125</v>
       </c>
       <c r="AZ3" t="n">
-        <v>40.74714107974742</v>
+        <v>496.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>39.29056852477449</v>
+        <v>497.23</v>
       </c>
       <c r="BB3" t="n">
-        <v>340</v>
+        <v>66.53058976891758</v>
       </c>
       <c r="BC3" t="n">
-        <v>340</v>
+        <v>54.88866509176149</v>
       </c>
       <c r="BD3" t="n">
-        <v>340</v>
+        <v>48.02238898420194</v>
       </c>
       <c r="BE3" t="n">
-        <v>340</v>
+        <v>43.97613443676013</v>
       </c>
       <c r="BF3" t="n">
-        <v>340</v>
+        <v>41.03059833831333</v>
       </c>
       <c r="BG3" t="n">
-        <v>340</v>
+        <v>39.12520196205291</v>
       </c>
       <c r="BH3" t="n">
-        <v>340</v>
+        <v>37.73105847226526</v>
       </c>
       <c r="BI3" t="n">
-        <v>340</v>
+        <v>37.00322808741001</v>
       </c>
       <c r="BJ3" t="n">
-        <v>340</v>
+        <v>36.18932301107607</v>
       </c>
       <c r="BK3" t="n">
-        <v>669</v>
+        <v>320</v>
       </c>
       <c r="BL3" t="n">
-        <v>669</v>
+        <v>320</v>
       </c>
       <c r="BM3" t="n">
-        <v>669</v>
+        <v>320</v>
       </c>
       <c r="BN3" t="n">
-        <v>669</v>
+        <v>320</v>
       </c>
       <c r="BO3" t="n">
-        <v>669</v>
+        <v>320</v>
       </c>
       <c r="BP3" t="n">
-        <v>669</v>
+        <v>320</v>
       </c>
       <c r="BQ3" t="n">
-        <v>669</v>
+        <v>320</v>
       </c>
       <c r="BR3" t="n">
-        <v>669</v>
+        <v>320</v>
       </c>
       <c r="BS3" t="n">
-        <v>669</v>
+        <v>320</v>
       </c>
       <c r="BT3" t="n">
-        <v>1</v>
+        <v>669</v>
       </c>
       <c r="BU3" t="n">
-        <v>1</v>
+        <v>669</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.9</v>
+        <v>669</v>
       </c>
       <c r="BW3" t="n">
-        <v>0.8214285714285714</v>
+        <v>669</v>
       </c>
       <c r="BX3" t="n">
-        <v>0.7567567567567568</v>
+        <v>669</v>
       </c>
       <c r="BY3" t="n">
-        <v>0.7173913043478261</v>
+        <v>669</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0.0196078431372549</v>
+        <v>669</v>
       </c>
       <c r="CA3" t="n">
-        <v>0.6666666666666666</v>
+        <v>669</v>
       </c>
       <c r="CB3" t="n">
-        <v>0.6964285714285714</v>
+        <v>669</v>
+      </c>
+      <c r="CC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI3" t="n">
+        <v>0.7391304347826086</v>
+      </c>
+      <c r="CJ3" t="n">
+        <v>0.7735849056603774</v>
+      </c>
+      <c r="CK3" t="n">
+        <v>0.7457627118644068</v>
+      </c>
+      <c r="CL3" t="n">
+        <v>496.04</v>
+      </c>
+      <c r="CM3" t="n">
+        <v>18.66</v>
       </c>
     </row>
     <row r="4">
@@ -1332,10 +1453,10 @@
         <v>499</v>
       </c>
       <c r="C4" t="n">
+        <v>32.61675315048184</v>
+      </c>
+      <c r="D4" t="n">
         <v>22</v>
-      </c>
-      <c r="D4" t="n">
-        <v>32.61675315048184</v>
       </c>
       <c r="E4" t="n">
         <v>499</v>
@@ -1344,228 +1465,261 @@
         <v>200</v>
       </c>
       <c r="G4" t="n">
-        <v>0.495</v>
-      </c>
-      <c r="H4" t="inlineStr">
+        <v>79.5</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="J4" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="K4" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="N4" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="O4" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="Q4" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I4" t="n">
-        <v>505.3137540546603</v>
-      </c>
-      <c r="J4" t="n">
-        <v>14.22180630881258</v>
-      </c>
-      <c r="K4" t="n">
-        <v>501.5635551295736</v>
-      </c>
-      <c r="L4" t="n">
-        <v>22.93682033980543</v>
-      </c>
-      <c r="M4" t="n">
-        <v>503.3169838970713</v>
-      </c>
-      <c r="N4" t="n">
-        <v>24.73025111196591</v>
-      </c>
-      <c r="O4" t="n">
-        <v>498.8932837308346</v>
-      </c>
-      <c r="P4" t="n">
-        <v>24.33600301468967</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>498.6954917977494</v>
-      </c>
       <c r="R4" t="n">
-        <v>26.89553446311331</v>
+        <v>505.31</v>
       </c>
       <c r="S4" t="n">
-        <v>499.6106234644749</v>
+        <v>14.22</v>
       </c>
       <c r="T4" t="n">
-        <v>25.64109510108371</v>
+        <v>501.56</v>
       </c>
       <c r="U4" t="n">
-        <v>500.2979629082263</v>
+        <v>22.94</v>
       </c>
       <c r="V4" t="n">
-        <v>25.53484559255301</v>
+        <v>503.32</v>
       </c>
       <c r="W4" t="n">
-        <v>499.529695615715</v>
+        <v>24.73</v>
       </c>
       <c r="X4" t="n">
-        <v>26.92424202361959</v>
+        <v>498.89</v>
       </c>
       <c r="Y4" t="n">
-        <v>500.4136620946969</v>
+        <v>24.34</v>
       </c>
       <c r="Z4" t="n">
-        <v>26.46522642736481</v>
+        <v>498.7</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>26.9</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>499.61</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>25.64</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>500.3</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>25.53</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>499.53</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>26.92</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>500.41</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>26.47</v>
       </c>
       <c r="AJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS4" t="n">
         <v>499.275</v>
       </c>
-      <c r="AK4" t="n">
+      <c r="AT4" t="n">
         <v>500.2</v>
       </c>
-      <c r="AL4" t="n">
+      <c r="AU4" t="n">
         <v>500.45</v>
       </c>
-      <c r="AM4" t="n">
+      <c r="AV4" t="n">
         <v>498.95</v>
       </c>
-      <c r="AN4" t="n">
+      <c r="AW4" t="n">
         <v>497.2833333333334</v>
       </c>
-      <c r="AO4" t="n">
+      <c r="AX4" t="n">
         <v>497.1285714285714</v>
       </c>
-      <c r="AP4" t="n">
+      <c r="AY4" t="n">
         <v>497.2125</v>
       </c>
-      <c r="AQ4" t="n">
+      <c r="AZ4" t="n">
         <v>498.1222222222222</v>
       </c>
-      <c r="AR4" t="n">
+      <c r="BA4" t="n">
         <v>498.385</v>
       </c>
-      <c r="AS4" t="n">
+      <c r="BB4" t="n">
         <v>68.02168312383927</v>
       </c>
-      <c r="AT4" t="n">
+      <c r="BC4" t="n">
         <v>57.77363874063441</v>
       </c>
-      <c r="AU4" t="n">
+      <c r="BD4" t="n">
         <v>52.02232693757556</v>
       </c>
-      <c r="AV4" t="n">
+      <c r="BE4" t="n">
         <v>49.289222959994</v>
       </c>
-      <c r="AW4" t="n">
+      <c r="BF4" t="n">
         <v>47.83568809534944</v>
       </c>
-      <c r="AX4" t="n">
+      <c r="BG4" t="n">
         <v>45.8858588327202</v>
       </c>
-      <c r="AY4" t="n">
+      <c r="BH4" t="n">
         <v>43.88442028499408</v>
       </c>
-      <c r="AZ4" t="n">
+      <c r="BI4" t="n">
         <v>42.3237069836694</v>
       </c>
-      <c r="BA4" t="n">
+      <c r="BJ4" t="n">
         <v>41.19656266000842</v>
       </c>
-      <c r="BB4" t="n">
+      <c r="BK4" t="n">
         <v>329</v>
       </c>
-      <c r="BC4" t="n">
+      <c r="BL4" t="n">
         <v>329</v>
       </c>
-      <c r="BD4" t="n">
+      <c r="BM4" t="n">
         <v>329</v>
       </c>
-      <c r="BE4" t="n">
+      <c r="BN4" t="n">
         <v>329</v>
       </c>
-      <c r="BF4" t="n">
+      <c r="BO4" t="n">
         <v>329</v>
       </c>
-      <c r="BG4" t="n">
+      <c r="BP4" t="n">
         <v>329</v>
       </c>
-      <c r="BH4" t="n">
+      <c r="BQ4" t="n">
         <v>329</v>
       </c>
-      <c r="BI4" t="n">
+      <c r="BR4" t="n">
         <v>329</v>
       </c>
-      <c r="BJ4" t="n">
+      <c r="BS4" t="n">
         <v>329</v>
       </c>
-      <c r="BK4" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ4" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR4" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS4" t="n">
-        <v>669</v>
-      </c>
       <c r="BT4" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY4" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ4" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA4" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB4" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC4" t="n">
         <v>0.8</v>
       </c>
-      <c r="BU4" t="n">
+      <c r="CD4" t="n">
         <v>0.6</v>
       </c>
-      <c r="BV4" t="n">
+      <c r="CE4" t="n">
         <v>0.6333333333333333</v>
       </c>
-      <c r="BW4" t="n">
+      <c r="CF4" t="n">
         <v>0.575</v>
       </c>
-      <c r="BX4" t="n">
+      <c r="CG4" t="n">
         <v>0.52</v>
       </c>
-      <c r="BY4" t="n">
+      <c r="CH4" t="n">
         <v>0.5</v>
       </c>
-      <c r="BZ4" t="n">
+      <c r="CI4" t="n">
         <v>0.5142857142857142</v>
       </c>
-      <c r="CA4" t="n">
+      <c r="CJ4" t="n">
         <v>0.4875</v>
       </c>
-      <c r="CB4" t="n">
+      <c r="CK4" t="n">
         <v>0.5287356321839081</v>
+      </c>
+      <c r="CL4" t="n">
+        <v>500.41</v>
+      </c>
+      <c r="CM4" t="n">
+        <v>26.47</v>
       </c>
     </row>
     <row r="5">
@@ -1578,10 +1732,10 @@
         <v>500</v>
       </c>
       <c r="C5" t="n">
+        <v>31.13417346182357</v>
+      </c>
+      <c r="D5" t="n">
         <v>21</v>
-      </c>
-      <c r="D5" t="n">
-        <v>31.13417346182357</v>
       </c>
       <c r="E5" t="n">
         <v>500</v>
@@ -1590,228 +1744,261 @@
         <v>200</v>
       </c>
       <c r="G5" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="H5" t="inlineStr">
+        <v>81</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="L5" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="M5" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="O5" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I5" t="n">
-        <v>494.261614218347</v>
-      </c>
-      <c r="J5" t="n">
-        <v>27.235847892901</v>
-      </c>
-      <c r="K5" t="n">
-        <v>498.2597673318786</v>
-      </c>
-      <c r="L5" t="n">
-        <v>30.48443335220029</v>
-      </c>
-      <c r="M5" t="n">
-        <v>498.3649986717213</v>
-      </c>
-      <c r="N5" t="n">
-        <v>31.70414766642364</v>
-      </c>
-      <c r="O5" t="n">
-        <v>500.3197628360084</v>
-      </c>
-      <c r="P5" t="n">
-        <v>32.48061483115941</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>499.2303290979897</v>
-      </c>
       <c r="R5" t="n">
-        <v>28.46845492840148</v>
+        <v>494.26</v>
       </c>
       <c r="S5" t="n">
-        <v>498.3600867932636</v>
+        <v>27.24</v>
       </c>
       <c r="T5" t="n">
-        <v>26.9434411349504</v>
+        <v>498.26</v>
       </c>
       <c r="U5" t="n">
-        <v>497.7685403255892</v>
+        <v>30.48</v>
       </c>
       <c r="V5" t="n">
-        <v>27.08872794101481</v>
+        <v>498.36</v>
       </c>
       <c r="W5" t="n">
-        <v>499.1199156276213</v>
+        <v>31.7</v>
       </c>
       <c r="X5" t="n">
-        <v>27.7855235005961</v>
+        <v>500.32</v>
       </c>
       <c r="Y5" t="n">
-        <v>500.3768897645408</v>
+        <v>32.48</v>
       </c>
       <c r="Z5" t="n">
-        <v>27.98552697807572</v>
+        <v>499.23</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>28.47</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>498.36</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>26.94</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>497.77</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>27.09</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>499.12</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>27.79</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>500.38</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>27.99</v>
       </c>
       <c r="AJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS5" t="n">
         <v>495.1</v>
       </c>
-      <c r="AK5" t="n">
+      <c r="AT5" t="n">
         <v>495.6166666666667</v>
       </c>
-      <c r="AL5" t="n">
+      <c r="AU5" t="n">
         <v>496.2875</v>
       </c>
-      <c r="AM5" t="n">
+      <c r="AV5" t="n">
         <v>494.99</v>
       </c>
-      <c r="AN5" t="n">
+      <c r="AW5" t="n">
         <v>495.75</v>
       </c>
-      <c r="AO5" t="n">
+      <c r="AX5" t="n">
         <v>496.3</v>
       </c>
-      <c r="AP5" t="n">
+      <c r="AY5" t="n">
         <v>494.7625</v>
       </c>
-      <c r="AQ5" t="n">
+      <c r="AZ5" t="n">
         <v>494.6388888888889</v>
       </c>
-      <c r="AR5" t="n">
+      <c r="BA5" t="n">
         <v>496.24</v>
       </c>
-      <c r="AS5" t="n">
+      <c r="BB5" t="n">
         <v>68.34208074093149</v>
       </c>
-      <c r="AT5" t="n">
+      <c r="BC5" t="n">
         <v>59.76679447839094</v>
       </c>
-      <c r="AU5" t="n">
+      <c r="BD5" t="n">
         <v>54.41925067244127</v>
       </c>
-      <c r="AV5" t="n">
+      <c r="BE5" t="n">
         <v>52.21733332907761</v>
       </c>
-      <c r="AW5" t="n">
+      <c r="BF5" t="n">
         <v>49.57305215537974</v>
       </c>
-      <c r="AX5" t="n">
+      <c r="BG5" t="n">
         <v>47.10682389147943</v>
       </c>
-      <c r="AY5" t="n">
+      <c r="BH5" t="n">
         <v>46.48595049851083</v>
       </c>
-      <c r="AZ5" t="n">
+      <c r="BI5" t="n">
         <v>44.98503008889474</v>
       </c>
-      <c r="BA5" t="n">
+      <c r="BJ5" t="n">
         <v>44.10456212230204</v>
       </c>
-      <c r="BB5" t="n">
+      <c r="BK5" t="n">
         <v>329</v>
       </c>
-      <c r="BC5" t="n">
+      <c r="BL5" t="n">
         <v>329</v>
       </c>
-      <c r="BD5" t="n">
+      <c r="BM5" t="n">
         <v>329</v>
       </c>
-      <c r="BE5" t="n">
+      <c r="BN5" t="n">
         <v>329</v>
       </c>
-      <c r="BF5" t="n">
+      <c r="BO5" t="n">
         <v>329</v>
       </c>
-      <c r="BG5" t="n">
+      <c r="BP5" t="n">
         <v>329</v>
       </c>
-      <c r="BH5" t="n">
+      <c r="BQ5" t="n">
         <v>329</v>
       </c>
-      <c r="BI5" t="n">
+      <c r="BR5" t="n">
         <v>329</v>
       </c>
-      <c r="BJ5" t="n">
+      <c r="BS5" t="n">
         <v>329</v>
       </c>
-      <c r="BK5" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP5" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ5" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR5" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS5" t="n">
-        <v>669</v>
-      </c>
       <c r="BT5" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY5" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ5" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA5" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB5" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC5" t="n">
         <v>0.6</v>
       </c>
-      <c r="BU5" t="n">
+      <c r="CD5" t="n">
         <v>0.8</v>
       </c>
-      <c r="BV5" t="n">
+      <c r="CE5" t="n">
         <v>0.7619047619047619</v>
       </c>
-      <c r="BW5" t="n">
+      <c r="CF5" t="n">
         <v>0.7931034482758621</v>
       </c>
-      <c r="BX5" t="n">
+      <c r="CG5" t="n">
         <v>0.6486486486486487</v>
       </c>
-      <c r="BY5" t="n">
+      <c r="CH5" t="n">
         <v>0.5555555555555556</v>
       </c>
-      <c r="BZ5" t="n">
+      <c r="CI5" t="n">
         <v>0.5098039215686274</v>
       </c>
-      <c r="CA5" t="n">
+      <c r="CJ5" t="n">
         <v>0.509090909090909</v>
       </c>
-      <c r="CB5" t="n">
+      <c r="CK5" t="n">
         <v>0.5087719298245614</v>
+      </c>
+      <c r="CL5" t="n">
+        <v>500.38</v>
+      </c>
+      <c r="CM5" t="n">
+        <v>27.99</v>
       </c>
     </row>
     <row r="6">
@@ -1824,10 +2011,10 @@
         <v>500</v>
       </c>
       <c r="C6" t="n">
+        <v>29.65159377316531</v>
+      </c>
+      <c r="D6" t="n">
         <v>20</v>
-      </c>
-      <c r="D6" t="n">
-        <v>29.65159377316531</v>
       </c>
       <c r="E6" t="n">
         <v>500</v>
@@ -1836,228 +2023,261 @@
         <v>200</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H6" t="inlineStr">
+        <v>83</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="L6" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="M6" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O6" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="Q6" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I6" t="n">
-        <v>482.9908201048159</v>
-      </c>
-      <c r="J6" t="n">
-        <v>20.85917439999978</v>
-      </c>
-      <c r="K6" t="n">
-        <v>491.0097895109787</v>
-      </c>
-      <c r="L6" t="n">
-        <v>22.8766938461405</v>
-      </c>
-      <c r="M6" t="n">
-        <v>499.2904916937989</v>
-      </c>
-      <c r="N6" t="n">
-        <v>23.66133507415041</v>
-      </c>
-      <c r="O6" t="n">
-        <v>499.9338927594912</v>
-      </c>
-      <c r="P6" t="n">
-        <v>22.97223182969984</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>501.7648491125319</v>
-      </c>
       <c r="R6" t="n">
-        <v>21.53216190531123</v>
+        <v>482.99</v>
       </c>
       <c r="S6" t="n">
-        <v>501.5279251321868</v>
+        <v>20.86</v>
       </c>
       <c r="T6" t="n">
-        <v>20.25241158971767</v>
+        <v>491.01</v>
       </c>
       <c r="U6" t="n">
-        <v>499.4393708930616</v>
+        <v>22.88</v>
       </c>
       <c r="V6" t="n">
-        <v>21.31433520732682</v>
+        <v>499.29</v>
       </c>
       <c r="W6" t="n">
-        <v>500.3610385750912</v>
+        <v>23.66</v>
       </c>
       <c r="X6" t="n">
-        <v>21.1596371183477</v>
+        <v>499.93</v>
       </c>
       <c r="Y6" t="n">
-        <v>499.6561447596011</v>
+        <v>22.97</v>
       </c>
       <c r="Z6" t="n">
-        <v>21.72968291279785</v>
+        <v>501.76</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>21.53</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>501.53</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>20.25</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>499.44</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>21.31</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>500.36</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>21.16</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>499.66</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>21.73</v>
       </c>
       <c r="AJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS6" t="n">
         <v>491.225</v>
       </c>
-      <c r="AK6" t="n">
+      <c r="AT6" t="n">
         <v>490.35</v>
       </c>
-      <c r="AL6" t="n">
+      <c r="AU6" t="n">
         <v>491.1625</v>
       </c>
-      <c r="AM6" t="n">
+      <c r="AV6" t="n">
         <v>493.23</v>
       </c>
-      <c r="AN6" t="n">
+      <c r="AW6" t="n">
         <v>494.8</v>
       </c>
-      <c r="AO6" t="n">
+      <c r="AX6" t="n">
         <v>496.1428571428572</v>
       </c>
-      <c r="AP6" t="n">
+      <c r="AY6" t="n">
         <v>496.95</v>
       </c>
-      <c r="AQ6" t="n">
+      <c r="AZ6" t="n">
         <v>498.0222222222222</v>
       </c>
-      <c r="AR6" t="n">
+      <c r="BA6" t="n">
         <v>498.64</v>
       </c>
-      <c r="AS6" t="n">
+      <c r="BB6" t="n">
         <v>68.82459135367242</v>
       </c>
-      <c r="AT6" t="n">
+      <c r="BC6" t="n">
         <v>58.65089513383406</v>
       </c>
-      <c r="AU6" t="n">
+      <c r="BD6" t="n">
         <v>53.17951761486747</v>
       </c>
-      <c r="AV6" t="n">
+      <c r="BE6" t="n">
         <v>49.03077706910222</v>
       </c>
-      <c r="AW6" t="n">
+      <c r="BF6" t="n">
         <v>45.79657920267262</v>
       </c>
-      <c r="AX6" t="n">
+      <c r="BG6" t="n">
         <v>43.27001129594284</v>
       </c>
-      <c r="AY6" t="n">
+      <c r="BH6" t="n">
         <v>41.42082809408812</v>
       </c>
-      <c r="AZ6" t="n">
+      <c r="BI6" t="n">
         <v>40.75331691416262</v>
       </c>
-      <c r="BA6" t="n">
+      <c r="BJ6" t="n">
         <v>40.35046963791127</v>
       </c>
-      <c r="BB6" t="n">
+      <c r="BK6" t="n">
         <v>323</v>
       </c>
-      <c r="BC6" t="n">
+      <c r="BL6" t="n">
         <v>323</v>
       </c>
-      <c r="BD6" t="n">
+      <c r="BM6" t="n">
         <v>323</v>
       </c>
-      <c r="BE6" t="n">
+      <c r="BN6" t="n">
         <v>323</v>
       </c>
-      <c r="BF6" t="n">
+      <c r="BO6" t="n">
         <v>323</v>
       </c>
-      <c r="BG6" t="n">
+      <c r="BP6" t="n">
         <v>323</v>
       </c>
-      <c r="BH6" t="n">
+      <c r="BQ6" t="n">
         <v>323</v>
       </c>
-      <c r="BI6" t="n">
+      <c r="BR6" t="n">
         <v>323</v>
       </c>
-      <c r="BJ6" t="n">
+      <c r="BS6" t="n">
         <v>323</v>
       </c>
-      <c r="BK6" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ6" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR6" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS6" t="n">
-        <v>669</v>
-      </c>
       <c r="BT6" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB6" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC6" t="n">
         <v>1</v>
       </c>
-      <c r="BU6" t="n">
+      <c r="CD6" t="n">
         <v>1</v>
       </c>
-      <c r="BV6" t="n">
+      <c r="CE6" t="n">
         <v>0.9</v>
       </c>
-      <c r="BW6" t="n">
+      <c r="CF6" t="n">
         <v>0.7241379310344828</v>
       </c>
-      <c r="BX6" t="n">
+      <c r="CG6" t="n">
         <v>0.631578947368421</v>
       </c>
-      <c r="BY6" t="n">
+      <c r="CH6" t="n">
         <v>0.6222222222222222</v>
       </c>
-      <c r="BZ6" t="n">
+      <c r="CI6" t="n">
         <v>0.62</v>
       </c>
-      <c r="CA6" t="n">
+      <c r="CJ6" t="n">
         <v>0.7</v>
       </c>
-      <c r="CB6" t="n">
+      <c r="CK6" t="n">
         <v>0.72</v>
+      </c>
+      <c r="CL6" t="n">
+        <v>499.66</v>
+      </c>
+      <c r="CM6" t="n">
+        <v>21.73</v>
       </c>
     </row>
     <row r="7">
@@ -2070,10 +2290,10 @@
         <v>498</v>
       </c>
       <c r="C7" t="n">
+        <v>28.16901408450704</v>
+      </c>
+      <c r="D7" t="n">
         <v>19</v>
-      </c>
-      <c r="D7" t="n">
-        <v>28.16901408450704</v>
       </c>
       <c r="E7" t="n">
         <v>498</v>
@@ -2082,244 +2302,277 @@
         <v>200</v>
       </c>
       <c r="G7" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="H7" t="inlineStr">
+        <v>82</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="K7" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="L7" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="M7" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="O7" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I7" t="n">
-        <v>505.2420617258209</v>
-      </c>
-      <c r="J7" t="n">
-        <v>14.83366293055597</v>
-      </c>
-      <c r="K7" t="n">
-        <v>503.4060292332783</v>
-      </c>
-      <c r="L7" t="n">
-        <v>17.85381440899507</v>
-      </c>
-      <c r="M7" t="n">
-        <v>505.7281411476015</v>
-      </c>
-      <c r="N7" t="n">
-        <v>18.93675370034147</v>
-      </c>
-      <c r="O7" t="n">
-        <v>502.2283527420956</v>
-      </c>
-      <c r="P7" t="n">
-        <v>23.96339722264051</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>502.3598025666287</v>
-      </c>
       <c r="R7" t="n">
-        <v>21.34159663407824</v>
+        <v>505.24</v>
       </c>
       <c r="S7" t="n">
-        <v>501.9377720255776</v>
+        <v>14.83</v>
       </c>
       <c r="T7" t="n">
-        <v>22.85248985361487</v>
+        <v>503.41</v>
       </c>
       <c r="U7" t="n">
-        <v>502.5886868011399</v>
+        <v>17.85</v>
       </c>
       <c r="V7" t="n">
-        <v>20.83616399921446</v>
+        <v>505.73</v>
       </c>
       <c r="W7" t="n">
-        <v>503.2540595294494</v>
+        <v>18.94</v>
       </c>
       <c r="X7" t="n">
-        <v>23.65447675166838</v>
+        <v>502.23</v>
       </c>
       <c r="Y7" t="n">
-        <v>503.478395012726</v>
+        <v>23.96</v>
       </c>
       <c r="Z7" t="n">
-        <v>24.14528793674507</v>
+        <v>502.36</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>21.34</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>501.94</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>22.85</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>502.59</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>20.84</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>503.25</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>23.65</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>503.48</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>24.15</v>
       </c>
       <c r="AJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS7" t="n">
         <v>498.275</v>
       </c>
-      <c r="AK7" t="n">
+      <c r="AT7" t="n">
         <v>499.4666666666666</v>
       </c>
-      <c r="AL7" t="n">
+      <c r="AU7" t="n">
         <v>502.1</v>
       </c>
-      <c r="AM7" t="n">
+      <c r="AV7" t="n">
         <v>501.73</v>
       </c>
-      <c r="AN7" t="n">
+      <c r="AW7" t="n">
         <v>500.375</v>
       </c>
-      <c r="AO7" t="n">
+      <c r="AX7" t="n">
         <v>500.3071428571429</v>
       </c>
-      <c r="AP7" t="n">
+      <c r="AY7" t="n">
         <v>500.15625</v>
       </c>
-      <c r="AQ7" t="n">
+      <c r="AZ7" t="n">
         <v>499.5444444444444</v>
       </c>
-      <c r="AR7" t="n">
+      <c r="BA7" t="n">
         <v>499.16</v>
       </c>
-      <c r="AS7" t="n">
+      <c r="BB7" t="n">
         <v>68.31068272971659</v>
       </c>
-      <c r="AT7" t="n">
+      <c r="BC7" t="n">
         <v>57.1376894488704</v>
       </c>
-      <c r="AU7" t="n">
+      <c r="BD7" t="n">
         <v>50.62054918706434</v>
       </c>
-      <c r="AV7" t="n">
+      <c r="BE7" t="n">
         <v>47.56844647452763</v>
       </c>
-      <c r="AW7" t="n">
+      <c r="BF7" t="n">
         <v>45.61671157591262</v>
       </c>
-      <c r="AX7" t="n">
+      <c r="BG7" t="n">
         <v>43.28706445324737</v>
       </c>
-      <c r="AY7" t="n">
+      <c r="BH7" t="n">
         <v>41.52326860854646</v>
       </c>
-      <c r="AZ7" t="n">
+      <c r="BI7" t="n">
         <v>41.0976239137742</v>
       </c>
-      <c r="BA7" t="n">
+      <c r="BJ7" t="n">
         <v>41.24105236290655</v>
       </c>
-      <c r="BB7" t="n">
+      <c r="BK7" t="n">
         <v>338</v>
       </c>
-      <c r="BC7" t="n">
+      <c r="BL7" t="n">
         <v>338</v>
       </c>
-      <c r="BD7" t="n">
+      <c r="BM7" t="n">
         <v>338</v>
       </c>
-      <c r="BE7" t="n">
+      <c r="BN7" t="n">
         <v>338</v>
       </c>
-      <c r="BF7" t="n">
+      <c r="BO7" t="n">
         <v>338</v>
       </c>
-      <c r="BG7" t="n">
+      <c r="BP7" t="n">
         <v>338</v>
       </c>
-      <c r="BH7" t="n">
+      <c r="BQ7" t="n">
         <v>338</v>
       </c>
-      <c r="BI7" t="n">
+      <c r="BR7" t="n">
         <v>338</v>
       </c>
-      <c r="BJ7" t="n">
+      <c r="BS7" t="n">
         <v>338</v>
       </c>
-      <c r="BK7" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ7" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR7" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS7" t="n">
-        <v>669</v>
-      </c>
       <c r="BT7" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB7" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC7" t="n">
         <v>0.9</v>
       </c>
-      <c r="BU7" t="n">
+      <c r="CD7" t="n">
         <v>1</v>
       </c>
-      <c r="BV7" t="n">
+      <c r="CE7" t="n">
         <v>0.6923076923076923</v>
       </c>
-      <c r="BW7" t="n">
+      <c r="CF7" t="n">
         <v>0.6363636363636364</v>
       </c>
-      <c r="BX7" t="n">
+      <c r="CG7" t="n">
         <v>0.5121951219512195</v>
       </c>
-      <c r="BY7" t="n">
+      <c r="CH7" t="n">
         <v>0.5102040816326531</v>
       </c>
-      <c r="BZ7" t="n">
+      <c r="CI7" t="n">
         <v>0.5172413793103449</v>
       </c>
-      <c r="CA7" t="n">
+      <c r="CJ7" t="n">
         <v>0.4769230769230769</v>
       </c>
-      <c r="CB7" t="n">
+      <c r="CK7" t="n">
         <v>0.4558823529411765</v>
+      </c>
+      <c r="CL7" t="n">
+        <v>503.48</v>
+      </c>
+      <c r="CM7" t="n">
+        <v>24.15</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S08_G4_502_21_REL2</t>
+          <t>S07_G4_502_21_REL2</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>502</v>
       </c>
       <c r="C8" t="n">
+        <v>31.13417346182357</v>
+      </c>
+      <c r="D8" t="n">
         <v>21</v>
-      </c>
-      <c r="D8" t="n">
-        <v>31.13417346182357</v>
       </c>
       <c r="E8" t="n">
         <v>502</v>
@@ -2328,244 +2581,277 @@
         <v>200</v>
       </c>
       <c r="G8" t="n">
-        <v>0.505</v>
-      </c>
-      <c r="H8" t="inlineStr">
+        <v>77.5</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="O8" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="Q8" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I8" t="n">
-        <v>498.7791031719503</v>
-      </c>
-      <c r="J8" t="n">
-        <v>19.65829599879192</v>
-      </c>
-      <c r="K8" t="n">
-        <v>501.5506539801665</v>
-      </c>
-      <c r="L8" t="n">
-        <v>16.77871298690012</v>
-      </c>
-      <c r="M8" t="n">
-        <v>509.8921074744549</v>
-      </c>
-      <c r="N8" t="n">
-        <v>17.38647997020758</v>
-      </c>
-      <c r="O8" t="n">
-        <v>508.0928900752518</v>
-      </c>
-      <c r="P8" t="n">
-        <v>16.78029950019437</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>504.9278358718917</v>
-      </c>
       <c r="R8" t="n">
-        <v>16.28165990475855</v>
+        <v>497.86</v>
       </c>
       <c r="S8" t="n">
-        <v>506.1518658508267</v>
+        <v>12.25</v>
       </c>
       <c r="T8" t="n">
-        <v>17.82205746919287</v>
+        <v>498.56</v>
       </c>
       <c r="U8" t="n">
-        <v>506.9109189429911</v>
+        <v>15.76</v>
       </c>
       <c r="V8" t="n">
-        <v>20.81736832184564</v>
+        <v>496.57</v>
       </c>
       <c r="W8" t="n">
-        <v>506.0901971412277</v>
+        <v>19.21</v>
       </c>
       <c r="X8" t="n">
-        <v>22.80072836988163</v>
+        <v>496.97</v>
       </c>
       <c r="Y8" t="n">
-        <v>505.7568902659561</v>
+        <v>19.72</v>
       </c>
       <c r="Z8" t="n">
-        <v>24.16368018504336</v>
+        <v>498.26</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>20.45</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>497.39</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>20.05</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>497.9</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>19.41</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>498.69</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>21.66</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>499.9</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>22.19</v>
       </c>
       <c r="AJ8" t="n">
-        <v>504.625</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>502.4666666666666</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>502.0625</v>
+        <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>502.96</v>
+        <v>0</v>
       </c>
       <c r="AN8" t="n">
-        <v>503.475</v>
+        <v>0</v>
       </c>
       <c r="AO8" t="n">
-        <v>504.0785714285714</v>
+        <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>505.19375</v>
+        <v>0</v>
       </c>
       <c r="AQ8" t="n">
-        <v>506.2388888888889</v>
+        <v>0</v>
       </c>
       <c r="AR8" t="n">
-        <v>506.565</v>
+        <v>0</v>
       </c>
       <c r="AS8" t="n">
-        <v>70.35008439938079</v>
+        <v>500.75</v>
       </c>
       <c r="AT8" t="n">
-        <v>58.99815439674552</v>
+        <v>501.4333333333333</v>
       </c>
       <c r="AU8" t="n">
-        <v>52.16208962215758</v>
+        <v>500.2625</v>
       </c>
       <c r="AV8" t="n">
-        <v>47.76105526472379</v>
+        <v>499.78</v>
       </c>
       <c r="AW8" t="n">
-        <v>44.44921493494945</v>
+        <v>499.65</v>
       </c>
       <c r="AX8" t="n">
-        <v>42.18040639530953</v>
+        <v>499.2071428571429</v>
       </c>
       <c r="AY8" t="n">
-        <v>40.86678004122052</v>
+        <v>498.74375</v>
       </c>
       <c r="AZ8" t="n">
-        <v>40.92586303832942</v>
+        <v>498.3666666666667</v>
       </c>
       <c r="BA8" t="n">
-        <v>41.61400935982977</v>
+        <v>497.905</v>
       </c>
       <c r="BB8" t="n">
-        <v>340</v>
+        <v>64.76640718767716</v>
       </c>
       <c r="BC8" t="n">
-        <v>340</v>
+        <v>53.93773158827583</v>
       </c>
       <c r="BD8" t="n">
-        <v>340</v>
+        <v>48.06057213298651</v>
       </c>
       <c r="BE8" t="n">
-        <v>340</v>
+        <v>44.46877106464716</v>
       </c>
       <c r="BF8" t="n">
-        <v>340</v>
+        <v>41.64405719907704</v>
       </c>
       <c r="BG8" t="n">
-        <v>340</v>
+        <v>39.64782401317368</v>
       </c>
       <c r="BH8" t="n">
-        <v>340</v>
+        <v>38.00629008384665</v>
       </c>
       <c r="BI8" t="n">
-        <v>340</v>
+        <v>36.59370012568952</v>
       </c>
       <c r="BJ8" t="n">
-        <v>340</v>
+        <v>35.80036277749151</v>
       </c>
       <c r="BK8" t="n">
-        <v>669</v>
+        <v>336</v>
       </c>
       <c r="BL8" t="n">
-        <v>669</v>
+        <v>336</v>
       </c>
       <c r="BM8" t="n">
-        <v>669</v>
+        <v>336</v>
       </c>
       <c r="BN8" t="n">
-        <v>669</v>
+        <v>336</v>
       </c>
       <c r="BO8" t="n">
-        <v>669</v>
+        <v>336</v>
       </c>
       <c r="BP8" t="n">
-        <v>669</v>
+        <v>336</v>
       </c>
       <c r="BQ8" t="n">
-        <v>669</v>
+        <v>336</v>
       </c>
       <c r="BR8" t="n">
-        <v>669</v>
+        <v>336</v>
       </c>
       <c r="BS8" t="n">
-        <v>669</v>
+        <v>336</v>
       </c>
       <c r="BT8" t="n">
-        <v>0.7142857142857143</v>
+        <v>669</v>
       </c>
       <c r="BU8" t="n">
-        <v>0.6666666666666666</v>
+        <v>669</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.875</v>
+        <v>669</v>
       </c>
       <c r="BW8" t="n">
-        <v>0.9545454545454546</v>
+        <v>669</v>
       </c>
       <c r="BX8" t="n">
-        <v>0.8275862068965517</v>
+        <v>669</v>
       </c>
       <c r="BY8" t="n">
-        <v>0.7894736842105263</v>
+        <v>669</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0.8333333333333334</v>
+        <v>669</v>
       </c>
       <c r="CA8" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB8" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC8" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="CD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE8" t="n">
+        <v>0.9047619047619048</v>
+      </c>
+      <c r="CF8" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="CG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH8" t="n">
+        <v>0.8947368421052632</v>
+      </c>
+      <c r="CI8" t="n">
         <v>1</v>
       </c>
-      <c r="CB8" t="n">
-        <v>0.9333333333333333</v>
+      <c r="CJ8" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="CK8" t="n">
+        <v>0.9629629629629629</v>
+      </c>
+      <c r="CL8" t="n">
+        <v>499.9</v>
+      </c>
+      <c r="CM8" t="n">
+        <v>22.19</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S07_G4_502_21_REL2</t>
+          <t>S08_G4_502_21_REL2</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>502</v>
       </c>
       <c r="C9" t="n">
+        <v>31.13417346182357</v>
+      </c>
+      <c r="D9" t="n">
         <v>21</v>
-      </c>
-      <c r="D9" t="n">
-        <v>31.13417346182357</v>
       </c>
       <c r="E9" t="n">
         <v>502</v>
@@ -2574,736 +2860,835 @@
         <v>200</v>
       </c>
       <c r="G9" t="n">
-        <v>0.485</v>
-      </c>
-      <c r="H9" t="inlineStr">
+        <v>82.5</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="L9" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="M9" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="N9" t="n">
+        <v>3</v>
+      </c>
+      <c r="O9" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="Q9" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I9" t="n">
-        <v>497.8605976596741</v>
-      </c>
-      <c r="J9" t="n">
-        <v>12.25180306537249</v>
-      </c>
-      <c r="K9" t="n">
-        <v>498.5608437697911</v>
-      </c>
-      <c r="L9" t="n">
-        <v>15.75575746023764</v>
-      </c>
-      <c r="M9" t="n">
-        <v>496.5701529678301</v>
-      </c>
-      <c r="N9" t="n">
-        <v>19.21288721609986</v>
-      </c>
-      <c r="O9" t="n">
-        <v>496.9737391916566</v>
-      </c>
-      <c r="P9" t="n">
-        <v>19.72205242129284</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>498.2602394261509</v>
-      </c>
       <c r="R9" t="n">
-        <v>20.45203756676226</v>
+        <v>498.78</v>
       </c>
       <c r="S9" t="n">
-        <v>497.3915902512767</v>
+        <v>19.66</v>
       </c>
       <c r="T9" t="n">
-        <v>20.04744542657872</v>
+        <v>501.55</v>
       </c>
       <c r="U9" t="n">
-        <v>497.9046398353881</v>
+        <v>16.78</v>
       </c>
       <c r="V9" t="n">
-        <v>19.41337931253222</v>
+        <v>509.89</v>
       </c>
       <c r="W9" t="n">
-        <v>498.6883272818915</v>
+        <v>17.39</v>
       </c>
       <c r="X9" t="n">
-        <v>21.66317433406095</v>
+        <v>508.09</v>
       </c>
       <c r="Y9" t="n">
-        <v>499.9029014887021</v>
+        <v>16.78</v>
       </c>
       <c r="Z9" t="n">
-        <v>22.18943626334134</v>
+        <v>504.93</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>16.28</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>506.15</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>17.82</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>506.91</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>20.82</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>506.09</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>22.8</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>505.76</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>24.16</v>
       </c>
       <c r="AJ9" t="n">
-        <v>500.75</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>501.4333333333333</v>
+        <v>0</v>
       </c>
       <c r="AL9" t="n">
-        <v>500.2625</v>
+        <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>499.78</v>
+        <v>0</v>
       </c>
       <c r="AN9" t="n">
-        <v>499.65</v>
+        <v>0</v>
       </c>
       <c r="AO9" t="n">
-        <v>499.2071428571429</v>
+        <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>498.74375</v>
+        <v>0</v>
       </c>
       <c r="AQ9" t="n">
-        <v>498.3666666666667</v>
+        <v>0</v>
       </c>
       <c r="AR9" t="n">
-        <v>497.905</v>
+        <v>0</v>
       </c>
       <c r="AS9" t="n">
-        <v>64.76640718767716</v>
+        <v>504.625</v>
       </c>
       <c r="AT9" t="n">
-        <v>53.93773158827583</v>
+        <v>502.4666666666666</v>
       </c>
       <c r="AU9" t="n">
-        <v>48.06057213298651</v>
+        <v>502.0625</v>
       </c>
       <c r="AV9" t="n">
-        <v>44.46877106464716</v>
+        <v>502.96</v>
       </c>
       <c r="AW9" t="n">
-        <v>41.64405719907704</v>
+        <v>503.475</v>
       </c>
       <c r="AX9" t="n">
-        <v>39.64782401317368</v>
+        <v>504.0785714285714</v>
       </c>
       <c r="AY9" t="n">
-        <v>38.00629008384665</v>
+        <v>505.19375</v>
       </c>
       <c r="AZ9" t="n">
-        <v>36.59370012568952</v>
+        <v>506.2388888888889</v>
       </c>
       <c r="BA9" t="n">
-        <v>35.80036277749151</v>
+        <v>506.565</v>
       </c>
       <c r="BB9" t="n">
-        <v>336</v>
+        <v>70.35008439938079</v>
       </c>
       <c r="BC9" t="n">
-        <v>336</v>
+        <v>58.99815439674552</v>
       </c>
       <c r="BD9" t="n">
-        <v>336</v>
+        <v>52.16208962215758</v>
       </c>
       <c r="BE9" t="n">
-        <v>336</v>
+        <v>47.76105526472379</v>
       </c>
       <c r="BF9" t="n">
-        <v>336</v>
+        <v>44.44921493494945</v>
       </c>
       <c r="BG9" t="n">
-        <v>336</v>
+        <v>42.18040639530953</v>
       </c>
       <c r="BH9" t="n">
-        <v>336</v>
+        <v>40.86678004122052</v>
       </c>
       <c r="BI9" t="n">
-        <v>336</v>
+        <v>40.92586303832942</v>
       </c>
       <c r="BJ9" t="n">
-        <v>336</v>
+        <v>41.61400935982977</v>
       </c>
       <c r="BK9" t="n">
-        <v>669</v>
+        <v>340</v>
       </c>
       <c r="BL9" t="n">
-        <v>669</v>
+        <v>340</v>
       </c>
       <c r="BM9" t="n">
-        <v>669</v>
+        <v>340</v>
       </c>
       <c r="BN9" t="n">
-        <v>669</v>
+        <v>340</v>
       </c>
       <c r="BO9" t="n">
-        <v>669</v>
+        <v>340</v>
       </c>
       <c r="BP9" t="n">
-        <v>669</v>
+        <v>340</v>
       </c>
       <c r="BQ9" t="n">
-        <v>669</v>
+        <v>340</v>
       </c>
       <c r="BR9" t="n">
-        <v>669</v>
+        <v>340</v>
       </c>
       <c r="BS9" t="n">
-        <v>669</v>
+        <v>340</v>
       </c>
       <c r="BT9" t="n">
-        <v>0.75</v>
+        <v>669</v>
       </c>
       <c r="BU9" t="n">
-        <v>0</v>
+        <v>669</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.9047619047619048</v>
+        <v>669</v>
       </c>
       <c r="BW9" t="n">
-        <v>0.9230769230769231</v>
+        <v>669</v>
       </c>
       <c r="BX9" t="n">
-        <v>0</v>
+        <v>669</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.8947368421052632</v>
+        <v>669</v>
       </c>
       <c r="BZ9" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB9" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC9" t="n">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="CD9" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="CE9" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="CF9" t="n">
+        <v>0.9545454545454546</v>
+      </c>
+      <c r="CG9" t="n">
+        <v>0.8275862068965517</v>
+      </c>
+      <c r="CH9" t="n">
+        <v>0.7894736842105263</v>
+      </c>
+      <c r="CI9" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="CJ9" t="n">
         <v>1</v>
       </c>
-      <c r="CA9" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="CB9" t="n">
-        <v>0.9629629629629629</v>
+      <c r="CK9" t="n">
+        <v>0.9333333333333333</v>
+      </c>
+      <c r="CL9" t="n">
+        <v>505.76</v>
+      </c>
+      <c r="CM9" t="n">
+        <v>24.16</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S10_G4_501_19_REL2</t>
+          <t>S09_G4_500_21_REL2</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C10" t="n">
-        <v>19</v>
+        <v>31.13417346182357</v>
       </c>
       <c r="D10" t="n">
-        <v>28.16901408450704</v>
+        <v>21</v>
       </c>
       <c r="E10" t="n">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="F10" t="n">
         <v>200</v>
       </c>
       <c r="G10" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="H10" t="inlineStr">
+        <v>80</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="M10" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="O10" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="Q10" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I10" t="n">
-        <v>503.7680023943157</v>
-      </c>
-      <c r="J10" t="n">
-        <v>19.81581323639481</v>
-      </c>
-      <c r="K10" t="n">
-        <v>506.38865973534</v>
-      </c>
-      <c r="L10" t="n">
-        <v>18.82034100321749</v>
-      </c>
-      <c r="M10" t="n">
-        <v>509.0460258863751</v>
-      </c>
-      <c r="N10" t="n">
-        <v>21.15624567171382</v>
-      </c>
-      <c r="O10" t="n">
-        <v>510.7179319397924</v>
-      </c>
-      <c r="P10" t="n">
-        <v>22.80780482466533</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>511.085607522327</v>
-      </c>
       <c r="R10" t="n">
-        <v>22.85909775820815</v>
+        <v>516.77</v>
       </c>
       <c r="S10" t="n">
-        <v>507.8403063205985</v>
+        <v>12.61</v>
       </c>
       <c r="T10" t="n">
-        <v>22.52511602179081</v>
+        <v>502.38</v>
       </c>
       <c r="U10" t="n">
-        <v>505.5037625183965</v>
+        <v>20.67</v>
       </c>
       <c r="V10" t="n">
-        <v>22.59726693580211</v>
+        <v>501.81</v>
       </c>
       <c r="W10" t="n">
-        <v>507.2187774787425</v>
+        <v>20.95</v>
       </c>
       <c r="X10" t="n">
-        <v>21.29352830900907</v>
+        <v>501.22</v>
       </c>
       <c r="Y10" t="n">
-        <v>507.3913087819831</v>
+        <v>24.24</v>
       </c>
       <c r="Z10" t="n">
-        <v>21.36954917311229</v>
+        <v>499.87</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>23.67</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>499.4</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>23.01</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>497.03</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>23.06</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>497.43</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>22.61</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>497.35</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>22.57</v>
       </c>
       <c r="AJ10" t="n">
-        <v>501.45</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>501.8833333333333</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>502.3125</v>
+        <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>503.74</v>
+        <v>0</v>
       </c>
       <c r="AN10" t="n">
-        <v>506.5666666666667</v>
+        <v>0</v>
       </c>
       <c r="AO10" t="n">
-        <v>506.9857142857143</v>
+        <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>506.7125</v>
+        <v>0</v>
       </c>
       <c r="AQ10" t="n">
-        <v>506.5222222222222</v>
+        <v>0</v>
       </c>
       <c r="AR10" t="n">
-        <v>506.375</v>
+        <v>0</v>
       </c>
       <c r="AS10" t="n">
-        <v>69.51185150749475</v>
+        <v>506.225</v>
       </c>
       <c r="AT10" t="n">
-        <v>58.47965220674814</v>
+        <v>507.8333333333333</v>
       </c>
       <c r="AU10" t="n">
-        <v>52.0568424296941</v>
+        <v>505.8</v>
       </c>
       <c r="AV10" t="n">
-        <v>48.60095060798709</v>
+        <v>504.4</v>
       </c>
       <c r="AW10" t="n">
-        <v>46.94744106149155</v>
+        <v>502.1666666666667</v>
       </c>
       <c r="AX10" t="n">
-        <v>44.79843519497491</v>
+        <v>500.3928571428572</v>
       </c>
       <c r="AY10" t="n">
-        <v>42.6623937883237</v>
+        <v>499.65625</v>
       </c>
       <c r="AZ10" t="n">
-        <v>40.86487972650511</v>
+        <v>499.7277777777778</v>
       </c>
       <c r="BA10" t="n">
-        <v>39.40348176240267</v>
+        <v>498.955</v>
       </c>
       <c r="BB10" t="n">
-        <v>342</v>
+        <v>67.36671563168268</v>
       </c>
       <c r="BC10" t="n">
-        <v>342</v>
+        <v>56.40365433393675</v>
       </c>
       <c r="BD10" t="n">
-        <v>342</v>
+        <v>50.7711532270048</v>
       </c>
       <c r="BE10" t="n">
-        <v>342</v>
+        <v>47.57499343142361</v>
       </c>
       <c r="BF10" t="n">
-        <v>342</v>
+        <v>45.72678524550888</v>
       </c>
       <c r="BG10" t="n">
-        <v>342</v>
+        <v>43.83079420234321</v>
       </c>
       <c r="BH10" t="n">
-        <v>342</v>
+        <v>42.37526502498244</v>
       </c>
       <c r="BI10" t="n">
-        <v>342</v>
+        <v>40.72793616119797</v>
       </c>
       <c r="BJ10" t="n">
-        <v>342</v>
+        <v>39.57363990082287</v>
       </c>
       <c r="BK10" t="n">
-        <v>669</v>
+        <v>335</v>
       </c>
       <c r="BL10" t="n">
-        <v>669</v>
+        <v>335</v>
       </c>
       <c r="BM10" t="n">
-        <v>669</v>
+        <v>335</v>
       </c>
       <c r="BN10" t="n">
-        <v>669</v>
+        <v>335</v>
       </c>
       <c r="BO10" t="n">
-        <v>669</v>
+        <v>335</v>
       </c>
       <c r="BP10" t="n">
-        <v>669</v>
+        <v>335</v>
       </c>
       <c r="BQ10" t="n">
-        <v>669</v>
+        <v>335</v>
       </c>
       <c r="BR10" t="n">
-        <v>669</v>
+        <v>335</v>
       </c>
       <c r="BS10" t="n">
-        <v>669</v>
+        <v>335</v>
       </c>
       <c r="BT10" t="n">
-        <v>0.875</v>
+        <v>669</v>
       </c>
       <c r="BU10" t="n">
-        <v>0.6470588235294118</v>
+        <v>669</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.5925925925925926</v>
+        <v>669</v>
       </c>
       <c r="BW10" t="n">
-        <v>0.5454545454545454</v>
+        <v>669</v>
       </c>
       <c r="BX10" t="n">
-        <v>0.696969696969697</v>
+        <v>669</v>
       </c>
       <c r="BY10" t="n">
-        <v>0.8</v>
+        <v>669</v>
       </c>
       <c r="BZ10" t="n">
-        <v>0.9714285714285714</v>
+        <v>669</v>
       </c>
       <c r="CA10" t="n">
-        <v>0.8974358974358975</v>
+        <v>669</v>
       </c>
       <c r="CB10" t="n">
-        <v>0.8372093023255814</v>
+        <v>669</v>
+      </c>
+      <c r="CC10" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD10" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="CE10" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="CF10" t="n">
+        <v>0.4736842105263158</v>
+      </c>
+      <c r="CG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH10" t="n">
+        <v>0.4038461538461539</v>
+      </c>
+      <c r="CI10" t="n">
+        <v>0.4807692307692308</v>
+      </c>
+      <c r="CJ10" t="n">
+        <v>0.5192307692307693</v>
+      </c>
+      <c r="CK10" t="n">
+        <v>0.5961538461538461</v>
+      </c>
+      <c r="CL10" t="n">
+        <v>497.35</v>
+      </c>
+      <c r="CM10" t="n">
+        <v>22.57</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S09_G4_500_21_REL2</t>
+          <t>S10_G4_501_19_REL2</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C11" t="n">
-        <v>21</v>
+        <v>28.16901408450704</v>
       </c>
       <c r="D11" t="n">
-        <v>31.13417346182357</v>
+        <v>19</v>
       </c>
       <c r="E11" t="n">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="F11" t="n">
         <v>200</v>
       </c>
       <c r="G11" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="H11" t="inlineStr">
+        <v>80</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="M11" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="O11" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="Q11" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I11" t="n">
-        <v>516.766065975114</v>
-      </c>
-      <c r="J11" t="n">
-        <v>12.61038969761715</v>
-      </c>
-      <c r="K11" t="n">
-        <v>502.3761897329218</v>
-      </c>
-      <c r="L11" t="n">
-        <v>20.66560489214898</v>
-      </c>
-      <c r="M11" t="n">
-        <v>501.8107177022752</v>
-      </c>
-      <c r="N11" t="n">
-        <v>20.95049993375513</v>
-      </c>
-      <c r="O11" t="n">
-        <v>501.2165483981113</v>
-      </c>
-      <c r="P11" t="n">
-        <v>24.24351186098872</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>499.8675174102731</v>
-      </c>
       <c r="R11" t="n">
-        <v>23.66945773512724</v>
+        <v>503.77</v>
       </c>
       <c r="S11" t="n">
-        <v>499.3992209691148</v>
+        <v>19.82</v>
       </c>
       <c r="T11" t="n">
-        <v>23.01387637690318</v>
+        <v>506.39</v>
       </c>
       <c r="U11" t="n">
-        <v>497.0304492263763</v>
+        <v>18.82</v>
       </c>
       <c r="V11" t="n">
-        <v>23.06000990375816</v>
+        <v>509.05</v>
       </c>
       <c r="W11" t="n">
-        <v>497.4324118135921</v>
+        <v>21.16</v>
       </c>
       <c r="X11" t="n">
-        <v>22.61403199441461</v>
+        <v>510.72</v>
       </c>
       <c r="Y11" t="n">
-        <v>497.349157192339</v>
+        <v>22.81</v>
       </c>
       <c r="Z11" t="n">
-        <v>22.56835243942204</v>
+        <v>511.09</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>22.86</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>507.84</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>22.53</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>505.5</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>22.6</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>507.22</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>21.29</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>507.39</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>21.37</v>
       </c>
       <c r="AJ11" t="n">
-        <v>506.225</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>507.8333333333333</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
-        <v>505.8</v>
+        <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>504.4</v>
+        <v>0</v>
       </c>
       <c r="AN11" t="n">
-        <v>502.1666666666667</v>
+        <v>0</v>
       </c>
       <c r="AO11" t="n">
-        <v>500.3928571428572</v>
+        <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>499.65625</v>
+        <v>0</v>
       </c>
       <c r="AQ11" t="n">
-        <v>499.7277777777778</v>
+        <v>0</v>
       </c>
       <c r="AR11" t="n">
-        <v>498.955</v>
+        <v>0</v>
       </c>
       <c r="AS11" t="n">
-        <v>67.36671563168268</v>
+        <v>501.45</v>
       </c>
       <c r="AT11" t="n">
-        <v>56.40365433393675</v>
+        <v>501.8833333333333</v>
       </c>
       <c r="AU11" t="n">
-        <v>50.7711532270048</v>
+        <v>502.3125</v>
       </c>
       <c r="AV11" t="n">
-        <v>47.57499343142361</v>
+        <v>503.74</v>
       </c>
       <c r="AW11" t="n">
-        <v>45.72678524550888</v>
+        <v>506.5666666666667</v>
       </c>
       <c r="AX11" t="n">
-        <v>43.83079420234321</v>
+        <v>506.9857142857143</v>
       </c>
       <c r="AY11" t="n">
-        <v>42.37526502498244</v>
+        <v>506.7125</v>
       </c>
       <c r="AZ11" t="n">
-        <v>40.72793616119797</v>
+        <v>506.5222222222222</v>
       </c>
       <c r="BA11" t="n">
-        <v>39.57363990082287</v>
+        <v>506.375</v>
       </c>
       <c r="BB11" t="n">
-        <v>335</v>
+        <v>69.51185150749475</v>
       </c>
       <c r="BC11" t="n">
-        <v>335</v>
+        <v>58.47965220674814</v>
       </c>
       <c r="BD11" t="n">
-        <v>335</v>
+        <v>52.0568424296941</v>
       </c>
       <c r="BE11" t="n">
-        <v>335</v>
+        <v>48.60095060798709</v>
       </c>
       <c r="BF11" t="n">
-        <v>335</v>
+        <v>46.94744106149155</v>
       </c>
       <c r="BG11" t="n">
-        <v>335</v>
+        <v>44.79843519497491</v>
       </c>
       <c r="BH11" t="n">
-        <v>335</v>
+        <v>42.6623937883237</v>
       </c>
       <c r="BI11" t="n">
-        <v>335</v>
+        <v>40.86487972650511</v>
       </c>
       <c r="BJ11" t="n">
-        <v>335</v>
+        <v>39.40348176240267</v>
       </c>
       <c r="BK11" t="n">
-        <v>669</v>
+        <v>342</v>
       </c>
       <c r="BL11" t="n">
-        <v>669</v>
+        <v>342</v>
       </c>
       <c r="BM11" t="n">
-        <v>669</v>
+        <v>342</v>
       </c>
       <c r="BN11" t="n">
-        <v>669</v>
+        <v>342</v>
       </c>
       <c r="BO11" t="n">
-        <v>669</v>
+        <v>342</v>
       </c>
       <c r="BP11" t="n">
-        <v>669</v>
+        <v>342</v>
       </c>
       <c r="BQ11" t="n">
-        <v>669</v>
+        <v>342</v>
       </c>
       <c r="BR11" t="n">
-        <v>669</v>
+        <v>342</v>
       </c>
       <c r="BS11" t="n">
-        <v>669</v>
+        <v>342</v>
       </c>
       <c r="BT11" t="n">
-        <v>1</v>
+        <v>669</v>
       </c>
       <c r="BU11" t="n">
-        <v>0.8333333333333334</v>
+        <v>669</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.5714285714285714</v>
+        <v>669</v>
       </c>
       <c r="BW11" t="n">
-        <v>0.4736842105263158</v>
+        <v>669</v>
       </c>
       <c r="BX11" t="n">
-        <v>0</v>
+        <v>669</v>
       </c>
       <c r="BY11" t="n">
-        <v>0.4038461538461539</v>
+        <v>669</v>
       </c>
       <c r="BZ11" t="n">
-        <v>0.4807692307692308</v>
+        <v>669</v>
       </c>
       <c r="CA11" t="n">
-        <v>0.5192307692307693</v>
+        <v>669</v>
       </c>
       <c r="CB11" t="n">
-        <v>0.5961538461538461</v>
+        <v>669</v>
+      </c>
+      <c r="CC11" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="CD11" t="n">
+        <v>0.6470588235294118</v>
+      </c>
+      <c r="CE11" t="n">
+        <v>0.5925925925925926</v>
+      </c>
+      <c r="CF11" t="n">
+        <v>0.5454545454545454</v>
+      </c>
+      <c r="CG11" t="n">
+        <v>0.696969696969697</v>
+      </c>
+      <c r="CH11" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="CI11" t="n">
+        <v>0.9714285714285714</v>
+      </c>
+      <c r="CJ11" t="n">
+        <v>0.8974358974358975</v>
+      </c>
+      <c r="CK11" t="n">
+        <v>0.8372093023255814</v>
+      </c>
+      <c r="CL11" t="n">
+        <v>507.39</v>
+      </c>
+      <c r="CM11" t="n">
+        <v>21.37</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>S12_G4_498_19_REL2</t>
+          <t>S11_G4_498_20_REL2</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>498</v>
       </c>
       <c r="C12" t="n">
-        <v>19</v>
+        <v>29.65159377316531</v>
       </c>
       <c r="D12" t="n">
-        <v>28.16901408450704</v>
+        <v>20</v>
       </c>
       <c r="E12" t="n">
         <v>498</v>
@@ -3312,244 +3697,277 @@
         <v>200</v>
       </c>
       <c r="G12" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="H12" t="inlineStr">
+        <v>80.5</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="L12" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="M12" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="N12" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="O12" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="Q12" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I12" t="n">
-        <v>498.2687730550547</v>
-      </c>
-      <c r="J12" t="n">
-        <v>7.952075540388884</v>
-      </c>
-      <c r="K12" t="n">
-        <v>498.4210448660185</v>
-      </c>
-      <c r="L12" t="n">
-        <v>14.45750873249302</v>
-      </c>
-      <c r="M12" t="n">
-        <v>494.3203839995485</v>
-      </c>
-      <c r="N12" t="n">
-        <v>18.47465186955634</v>
-      </c>
-      <c r="O12" t="n">
-        <v>489.0372598666277</v>
-      </c>
-      <c r="P12" t="n">
-        <v>24.37830928480378</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>490.4774109631501</v>
-      </c>
       <c r="R12" t="n">
-        <v>21.82660696392552</v>
+        <v>484.64</v>
       </c>
       <c r="S12" t="n">
-        <v>491.8635027533609</v>
+        <v>22.32</v>
       </c>
       <c r="T12" t="n">
-        <v>20.94545208207472</v>
+        <v>496.33</v>
       </c>
       <c r="U12" t="n">
-        <v>492.7765919761446</v>
+        <v>21.94</v>
       </c>
       <c r="V12" t="n">
-        <v>22.16924794504644</v>
+        <v>492.32</v>
       </c>
       <c r="W12" t="n">
-        <v>492.7009129240983</v>
+        <v>27.85</v>
       </c>
       <c r="X12" t="n">
-        <v>21.45287111147502</v>
+        <v>495.67</v>
       </c>
       <c r="Y12" t="n">
-        <v>494.0098928493818</v>
+        <v>25.41</v>
       </c>
       <c r="Z12" t="n">
-        <v>21.59291621589803</v>
+        <v>496</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>24.7</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>497.2</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>24.83</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>498.98</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>26.84</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>499.77</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>25.61</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>498.27</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AJ12" t="n">
-        <v>499.075</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>498.8833333333333</v>
+        <v>0</v>
       </c>
       <c r="AL12" t="n">
-        <v>497.4875</v>
+        <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>493.69</v>
+        <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>491.7</v>
+        <v>0</v>
       </c>
       <c r="AO12" t="n">
-        <v>491.1071428571428</v>
+        <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>490.83125</v>
+        <v>0</v>
       </c>
       <c r="AQ12" t="n">
-        <v>491.4111111111111</v>
+        <v>0</v>
       </c>
       <c r="AR12" t="n">
-        <v>491.625</v>
+        <v>0</v>
       </c>
       <c r="AS12" t="n">
-        <v>66.50991937297775</v>
+        <v>487.05</v>
       </c>
       <c r="AT12" t="n">
-        <v>55.33175449554764</v>
+        <v>490.2166666666666</v>
       </c>
       <c r="AU12" t="n">
-        <v>49.15943290712374</v>
+        <v>492.9875</v>
       </c>
       <c r="AV12" t="n">
-        <v>47.54885803045116</v>
+        <v>494.2</v>
       </c>
       <c r="AW12" t="n">
-        <v>45.26010016191598</v>
+        <v>494.6083333333333</v>
       </c>
       <c r="AX12" t="n">
-        <v>42.87368430777146</v>
+        <v>495.0214285714285</v>
       </c>
       <c r="AY12" t="n">
-        <v>40.97731413157163</v>
+        <v>495.5125</v>
       </c>
       <c r="AZ12" t="n">
-        <v>39.8659962163369</v>
+        <v>496.5944444444444</v>
       </c>
       <c r="BA12" t="n">
-        <v>38.79696347654028</v>
+        <v>496.56</v>
       </c>
       <c r="BB12" t="n">
-        <v>335</v>
+        <v>71.87104771742234</v>
       </c>
       <c r="BC12" t="n">
-        <v>335</v>
+        <v>60.77227757968449</v>
       </c>
       <c r="BD12" t="n">
-        <v>335</v>
+        <v>54.03389994947616</v>
       </c>
       <c r="BE12" t="n">
-        <v>335</v>
+        <v>49.60564484007843</v>
       </c>
       <c r="BF12" t="n">
-        <v>335</v>
+        <v>46.45540797964814</v>
       </c>
       <c r="BG12" t="n">
-        <v>335</v>
+        <v>44.02669123175539</v>
       </c>
       <c r="BH12" t="n">
-        <v>335</v>
+        <v>42.44304823819797</v>
       </c>
       <c r="BI12" t="n">
-        <v>335</v>
+        <v>41.38648427019277</v>
       </c>
       <c r="BJ12" t="n">
-        <v>335</v>
+        <v>40.94797186674818</v>
       </c>
       <c r="BK12" t="n">
-        <v>669</v>
+        <v>333</v>
       </c>
       <c r="BL12" t="n">
-        <v>669</v>
+        <v>333</v>
       </c>
       <c r="BM12" t="n">
-        <v>669</v>
+        <v>333</v>
       </c>
       <c r="BN12" t="n">
-        <v>669</v>
+        <v>333</v>
       </c>
       <c r="BO12" t="n">
-        <v>669</v>
+        <v>333</v>
       </c>
       <c r="BP12" t="n">
-        <v>669</v>
+        <v>333</v>
       </c>
       <c r="BQ12" t="n">
-        <v>669</v>
+        <v>333</v>
       </c>
       <c r="BR12" t="n">
-        <v>669</v>
+        <v>333</v>
       </c>
       <c r="BS12" t="n">
-        <v>669</v>
+        <v>333</v>
       </c>
       <c r="BT12" t="n">
-        <v>0.2222222222222222</v>
+        <v>669</v>
       </c>
       <c r="BU12" t="n">
-        <v>0.1176470588235294</v>
+        <v>669</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.5925925925925926</v>
+        <v>669</v>
       </c>
       <c r="BW12" t="n">
-        <v>0.4444444444444444</v>
+        <v>669</v>
       </c>
       <c r="BX12" t="n">
-        <v>0.3777777777777778</v>
+        <v>669</v>
       </c>
       <c r="BY12" t="n">
-        <v>0.3962264150943396</v>
+        <v>669</v>
       </c>
       <c r="BZ12" t="n">
-        <v>0.01587301587301587</v>
+        <v>669</v>
       </c>
       <c r="CA12" t="n">
-        <v>0.4603174603174603</v>
+        <v>669</v>
       </c>
       <c r="CB12" t="n">
-        <v>0.5384615384615384</v>
+        <v>669</v>
+      </c>
+      <c r="CC12" t="n">
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="CD12" t="n">
+        <v>0.6153846153846154</v>
+      </c>
+      <c r="CE12" t="n">
+        <v>0.631578947368421</v>
+      </c>
+      <c r="CF12" t="n">
+        <v>0.6206896551724138</v>
+      </c>
+      <c r="CG12" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="CH12" t="n">
+        <v>0.673469387755102</v>
+      </c>
+      <c r="CI12" t="n">
+        <v>0.6271186440677966</v>
+      </c>
+      <c r="CJ12" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="CK12" t="n">
+        <v>0.6142857142857143</v>
+      </c>
+      <c r="CL12" t="n">
+        <v>498.27</v>
+      </c>
+      <c r="CM12" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>S11_G4_498_20_REL2</t>
+          <t>S12_G4_498_19_REL2</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>498</v>
       </c>
       <c r="C13" t="n">
-        <v>20</v>
+        <v>28.16901408450704</v>
       </c>
       <c r="D13" t="n">
-        <v>29.65159377316531</v>
+        <v>19</v>
       </c>
       <c r="E13" t="n">
         <v>498</v>
@@ -3558,228 +3976,261 @@
         <v>200</v>
       </c>
       <c r="G13" t="n">
-        <v>0.495</v>
-      </c>
-      <c r="H13" t="inlineStr">
+        <v>81</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="J13" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="L13" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="M13" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="N13" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="O13" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q13" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I13" t="n">
-        <v>484.6436840345236</v>
-      </c>
-      <c r="J13" t="n">
-        <v>22.32055511774104</v>
-      </c>
-      <c r="K13" t="n">
-        <v>496.3345222920385</v>
-      </c>
-      <c r="L13" t="n">
-        <v>21.94279741003012</v>
-      </c>
-      <c r="M13" t="n">
-        <v>492.3233799748913</v>
-      </c>
-      <c r="N13" t="n">
-        <v>27.85373310251661</v>
-      </c>
-      <c r="O13" t="n">
-        <v>495.6731811983894</v>
-      </c>
-      <c r="P13" t="n">
-        <v>25.40659292643425</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>495.998789394243</v>
-      </c>
       <c r="R13" t="n">
-        <v>24.70086050888767</v>
+        <v>498.27</v>
       </c>
       <c r="S13" t="n">
-        <v>497.1977149461453</v>
+        <v>7.95</v>
       </c>
       <c r="T13" t="n">
-        <v>24.83418365737002</v>
+        <v>498.42</v>
       </c>
       <c r="U13" t="n">
-        <v>498.981877033591</v>
+        <v>14.46</v>
       </c>
       <c r="V13" t="n">
-        <v>26.84195331006914</v>
+        <v>494.32</v>
       </c>
       <c r="W13" t="n">
-        <v>499.7745486459797</v>
+        <v>18.47</v>
       </c>
       <c r="X13" t="n">
-        <v>25.6078070988635</v>
+        <v>489.04</v>
       </c>
       <c r="Y13" t="n">
-        <v>498.2681768547851</v>
+        <v>24.38</v>
       </c>
       <c r="Z13" t="n">
-        <v>24.998757547489</v>
+        <v>490.48</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>21.83</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>491.86</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>20.95</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>492.78</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>22.17</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>492.7</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>21.45</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>494.01</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>21.59</v>
       </c>
       <c r="AJ13" t="n">
-        <v>487.05</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>490.2166666666666</v>
+        <v>0</v>
       </c>
       <c r="AL13" t="n">
-        <v>492.9875</v>
+        <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>494.2</v>
+        <v>0</v>
       </c>
       <c r="AN13" t="n">
-        <v>494.6083333333333</v>
+        <v>0</v>
       </c>
       <c r="AO13" t="n">
-        <v>495.0214285714285</v>
+        <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>495.5125</v>
+        <v>0</v>
       </c>
       <c r="AQ13" t="n">
-        <v>496.5944444444444</v>
+        <v>0</v>
       </c>
       <c r="AR13" t="n">
-        <v>496.56</v>
+        <v>0</v>
       </c>
       <c r="AS13" t="n">
-        <v>71.87104771742234</v>
+        <v>499.075</v>
       </c>
       <c r="AT13" t="n">
-        <v>60.77227757968449</v>
+        <v>498.8833333333333</v>
       </c>
       <c r="AU13" t="n">
-        <v>54.03389994947616</v>
+        <v>497.4875</v>
       </c>
       <c r="AV13" t="n">
-        <v>49.60564484007843</v>
+        <v>493.69</v>
       </c>
       <c r="AW13" t="n">
-        <v>46.45540797964814</v>
+        <v>491.7</v>
       </c>
       <c r="AX13" t="n">
-        <v>44.02669123175539</v>
+        <v>491.1071428571428</v>
       </c>
       <c r="AY13" t="n">
-        <v>42.44304823819797</v>
+        <v>490.83125</v>
       </c>
       <c r="AZ13" t="n">
-        <v>41.38648427019277</v>
+        <v>491.4111111111111</v>
       </c>
       <c r="BA13" t="n">
-        <v>40.94797186674818</v>
+        <v>491.625</v>
       </c>
       <c r="BB13" t="n">
-        <v>333</v>
+        <v>66.50991937297775</v>
       </c>
       <c r="BC13" t="n">
-        <v>333</v>
+        <v>55.33175449554764</v>
       </c>
       <c r="BD13" t="n">
-        <v>333</v>
+        <v>49.15943290712374</v>
       </c>
       <c r="BE13" t="n">
-        <v>333</v>
+        <v>47.54885803045116</v>
       </c>
       <c r="BF13" t="n">
-        <v>333</v>
+        <v>45.26010016191598</v>
       </c>
       <c r="BG13" t="n">
-        <v>333</v>
+        <v>42.87368430777146</v>
       </c>
       <c r="BH13" t="n">
-        <v>333</v>
+        <v>40.97731413157163</v>
       </c>
       <c r="BI13" t="n">
-        <v>333</v>
+        <v>39.8659962163369</v>
       </c>
       <c r="BJ13" t="n">
-        <v>333</v>
+        <v>38.79696347654028</v>
       </c>
       <c r="BK13" t="n">
-        <v>669</v>
+        <v>335</v>
       </c>
       <c r="BL13" t="n">
-        <v>669</v>
+        <v>335</v>
       </c>
       <c r="BM13" t="n">
-        <v>669</v>
+        <v>335</v>
       </c>
       <c r="BN13" t="n">
-        <v>669</v>
+        <v>335</v>
       </c>
       <c r="BO13" t="n">
-        <v>669</v>
+        <v>335</v>
       </c>
       <c r="BP13" t="n">
-        <v>669</v>
+        <v>335</v>
       </c>
       <c r="BQ13" t="n">
-        <v>669</v>
+        <v>335</v>
       </c>
       <c r="BR13" t="n">
-        <v>669</v>
+        <v>335</v>
       </c>
       <c r="BS13" t="n">
-        <v>669</v>
+        <v>335</v>
       </c>
       <c r="BT13" t="n">
-        <v>0.8888888888888888</v>
+        <v>669</v>
       </c>
       <c r="BU13" t="n">
-        <v>0.6153846153846154</v>
+        <v>669</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.631578947368421</v>
+        <v>669</v>
       </c>
       <c r="BW13" t="n">
-        <v>0.6206896551724138</v>
+        <v>669</v>
       </c>
       <c r="BX13" t="n">
-        <v>0.6666666666666666</v>
+        <v>669</v>
       </c>
       <c r="BY13" t="n">
-        <v>0.673469387755102</v>
+        <v>669</v>
       </c>
       <c r="BZ13" t="n">
-        <v>0.6271186440677966</v>
+        <v>669</v>
       </c>
       <c r="CA13" t="n">
-        <v>0.625</v>
+        <v>669</v>
       </c>
       <c r="CB13" t="n">
-        <v>0.6142857142857143</v>
+        <v>669</v>
+      </c>
+      <c r="CC13" t="n">
+        <v>0.2222222222222222</v>
+      </c>
+      <c r="CD13" t="n">
+        <v>0.1176470588235294</v>
+      </c>
+      <c r="CE13" t="n">
+        <v>0.5925925925925926</v>
+      </c>
+      <c r="CF13" t="n">
+        <v>0.4444444444444444</v>
+      </c>
+      <c r="CG13" t="n">
+        <v>0.3777777777777778</v>
+      </c>
+      <c r="CH13" t="n">
+        <v>0.3962264150943396</v>
+      </c>
+      <c r="CI13" t="n">
+        <v>0.01587301587301587</v>
+      </c>
+      <c r="CJ13" t="n">
+        <v>0.4603174603174603</v>
+      </c>
+      <c r="CK13" t="n">
+        <v>0.5384615384615384</v>
+      </c>
+      <c r="CL13" t="n">
+        <v>494.01</v>
+      </c>
+      <c r="CM13" t="n">
+        <v>21.59</v>
       </c>
     </row>
     <row r="14">
@@ -3792,10 +4243,10 @@
         <v>502</v>
       </c>
       <c r="C14" t="n">
+        <v>32.61675315048184</v>
+      </c>
+      <c r="D14" t="n">
         <v>22</v>
-      </c>
-      <c r="D14" t="n">
-        <v>32.61675315048184</v>
       </c>
       <c r="E14" t="n">
         <v>502</v>
@@ -3804,228 +4255,261 @@
         <v>200</v>
       </c>
       <c r="G14" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="H14" t="inlineStr">
+        <v>81</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="I14" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="L14" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="M14" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="N14" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="O14" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="Q14" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I14" t="n">
-        <v>500.4305368379914</v>
-      </c>
-      <c r="J14" t="n">
-        <v>16.72494430428258</v>
-      </c>
-      <c r="K14" t="n">
-        <v>504.894907444312</v>
-      </c>
-      <c r="L14" t="n">
-        <v>18.75928721104155</v>
-      </c>
-      <c r="M14" t="n">
-        <v>507.7185761397166</v>
-      </c>
-      <c r="N14" t="n">
-        <v>18.60059722528993</v>
-      </c>
-      <c r="O14" t="n">
-        <v>510.4353333810465</v>
-      </c>
-      <c r="P14" t="n">
-        <v>16.85425534100549</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>507.762797677165</v>
-      </c>
       <c r="R14" t="n">
-        <v>19.78910440133336</v>
+        <v>500.43</v>
       </c>
       <c r="S14" t="n">
-        <v>507.1802805658375</v>
+        <v>16.72</v>
       </c>
       <c r="T14" t="n">
-        <v>20.41750157458993</v>
+        <v>504.89</v>
       </c>
       <c r="U14" t="n">
-        <v>505.7568661683645</v>
+        <v>18.76</v>
       </c>
       <c r="V14" t="n">
-        <v>20.57884820630897</v>
+        <v>507.72</v>
       </c>
       <c r="W14" t="n">
-        <v>504.4388839707079</v>
+        <v>18.6</v>
       </c>
       <c r="X14" t="n">
-        <v>22.47999289383075</v>
+        <v>510.44</v>
       </c>
       <c r="Y14" t="n">
-        <v>503.4219985104547</v>
+        <v>16.85</v>
       </c>
       <c r="Z14" t="n">
-        <v>24.96176356658717</v>
+        <v>507.76</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>19.79</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>507.18</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>20.42</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>505.76</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>20.58</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>504.44</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>22.48</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>503.42</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>24.96</v>
       </c>
       <c r="AJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS14" t="n">
         <v>499.7</v>
       </c>
-      <c r="AK14" t="n">
+      <c r="AT14" t="n">
         <v>501.75</v>
       </c>
-      <c r="AL14" t="n">
+      <c r="AU14" t="n">
         <v>503.8375</v>
       </c>
-      <c r="AM14" t="n">
+      <c r="AV14" t="n">
         <v>505.07</v>
       </c>
-      <c r="AN14" t="n">
+      <c r="AW14" t="n">
         <v>505.7583333333333</v>
       </c>
-      <c r="AO14" t="n">
+      <c r="AX14" t="n">
         <v>505.35</v>
       </c>
-      <c r="AP14" t="n">
+      <c r="AY14" t="n">
         <v>503.775</v>
       </c>
-      <c r="AQ14" t="n">
+      <c r="AZ14" t="n">
         <v>501.6166666666667</v>
       </c>
-      <c r="AR14" t="n">
+      <c r="BA14" t="n">
         <v>500.165</v>
       </c>
-      <c r="AS14" t="n">
+      <c r="BB14" t="n">
         <v>65.78495268676569</v>
       </c>
-      <c r="AT14" t="n">
+      <c r="BC14" t="n">
         <v>54.61154487224595</v>
       </c>
-      <c r="AU14" t="n">
+      <c r="BD14" t="n">
         <v>48.85602412957894</v>
       </c>
-      <c r="AV14" t="n">
+      <c r="BE14" t="n">
         <v>44.83040374567242</v>
       </c>
-      <c r="AW14" t="n">
+      <c r="BF14" t="n">
         <v>41.87322052603814</v>
       </c>
-      <c r="AX14" t="n">
+      <c r="BG14" t="n">
         <v>40.04924201173208</v>
       </c>
-      <c r="AY14" t="n">
+      <c r="BH14" t="n">
         <v>39.47625077182482</v>
       </c>
-      <c r="AZ14" t="n">
+      <c r="BI14" t="n">
         <v>39.60012275514082</v>
       </c>
-      <c r="BA14" t="n">
+      <c r="BJ14" t="n">
         <v>40.87233508132366</v>
       </c>
-      <c r="BB14" t="n">
+      <c r="BK14" t="n">
         <v>326</v>
       </c>
-      <c r="BC14" t="n">
+      <c r="BL14" t="n">
         <v>326</v>
       </c>
-      <c r="BD14" t="n">
+      <c r="BM14" t="n">
         <v>326</v>
       </c>
-      <c r="BE14" t="n">
+      <c r="BN14" t="n">
         <v>326</v>
       </c>
-      <c r="BF14" t="n">
+      <c r="BO14" t="n">
         <v>326</v>
       </c>
-      <c r="BG14" t="n">
+      <c r="BP14" t="n">
         <v>326</v>
       </c>
-      <c r="BH14" t="n">
+      <c r="BQ14" t="n">
         <v>326</v>
       </c>
-      <c r="BI14" t="n">
+      <c r="BR14" t="n">
         <v>326</v>
       </c>
-      <c r="BJ14" t="n">
+      <c r="BS14" t="n">
         <v>326</v>
       </c>
-      <c r="BK14" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL14" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM14" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN14" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO14" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP14" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ14" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR14" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS14" t="n">
-        <v>669</v>
-      </c>
       <c r="BT14" t="n">
-        <v>0</v>
+        <v>669</v>
       </c>
       <c r="BU14" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW14" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX14" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY14" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ14" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA14" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB14" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD14" t="n">
         <v>0.631578947368421</v>
       </c>
-      <c r="BV14" t="n">
+      <c r="CE14" t="n">
         <v>0.75</v>
       </c>
-      <c r="BW14" t="n">
+      <c r="CF14" t="n">
         <v>0.7419354838709677</v>
       </c>
-      <c r="BX14" t="n">
+      <c r="CG14" t="n">
         <v>0.7368421052631579</v>
       </c>
-      <c r="BY14" t="n">
+      <c r="CH14" t="n">
         <v>0.6739130434782609</v>
       </c>
-      <c r="BZ14" t="n">
+      <c r="CI14" t="n">
         <v>0.5961538461538461</v>
       </c>
-      <c r="CA14" t="n">
+      <c r="CJ14" t="n">
         <v>0.5849056603773585</v>
       </c>
-      <c r="CB14" t="n">
+      <c r="CK14" t="n">
         <v>0.5535714285714286</v>
+      </c>
+      <c r="CL14" t="n">
+        <v>503.42</v>
+      </c>
+      <c r="CM14" t="n">
+        <v>24.96</v>
       </c>
     </row>
     <row r="15">
@@ -4038,10 +4522,10 @@
         <v>500</v>
       </c>
       <c r="C15" t="n">
+        <v>29.65159377316531</v>
+      </c>
+      <c r="D15" t="n">
         <v>20</v>
-      </c>
-      <c r="D15" t="n">
-        <v>29.65159377316531</v>
       </c>
       <c r="E15" t="n">
         <v>500</v>
@@ -4050,720 +4534,819 @@
         <v>200</v>
       </c>
       <c r="G15" t="n">
-        <v>0.505</v>
-      </c>
-      <c r="H15" t="inlineStr">
+        <v>82.5</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="L15" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="M15" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="N15" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="O15" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="Q15" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I15" t="n">
-        <v>494.9090464090566</v>
-      </c>
-      <c r="J15" t="n">
-        <v>34.46542306473837</v>
-      </c>
-      <c r="K15" t="n">
-        <v>496.3777508635812</v>
-      </c>
-      <c r="L15" t="n">
-        <v>33.22292141804382</v>
-      </c>
-      <c r="M15" t="n">
-        <v>498.2628351538831</v>
-      </c>
-      <c r="N15" t="n">
-        <v>35.51816745905295</v>
-      </c>
-      <c r="O15" t="n">
-        <v>497.645163680187</v>
-      </c>
-      <c r="P15" t="n">
-        <v>29.4339751472223</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>495.9521888013634</v>
-      </c>
       <c r="R15" t="n">
-        <v>28.98389843441493</v>
+        <v>494.91</v>
       </c>
       <c r="S15" t="n">
-        <v>496.081323908506</v>
+        <v>34.47</v>
       </c>
       <c r="T15" t="n">
-        <v>27.02742870301502</v>
+        <v>496.38</v>
       </c>
       <c r="U15" t="n">
-        <v>497.1210641509165</v>
+        <v>33.22</v>
       </c>
       <c r="V15" t="n">
-        <v>26.54708426759693</v>
+        <v>498.26</v>
       </c>
       <c r="W15" t="n">
-        <v>496.1485829712713</v>
+        <v>35.52</v>
       </c>
       <c r="X15" t="n">
-        <v>25.27651971569177</v>
+        <v>497.65</v>
       </c>
       <c r="Y15" t="n">
-        <v>496.3666059891158</v>
+        <v>29.43</v>
       </c>
       <c r="Z15" t="n">
-        <v>25.02364058599532</v>
+        <v>495.95</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>28.98</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>496.08</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>27.03</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>497.12</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>26.55</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>496.15</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>25.28</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>496.37</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>25.02</v>
       </c>
       <c r="AJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS15" t="n">
         <v>498.95</v>
       </c>
-      <c r="AK15" t="n">
+      <c r="AT15" t="n">
         <v>495.7</v>
       </c>
-      <c r="AL15" t="n">
+      <c r="AU15" t="n">
         <v>495.425</v>
       </c>
-      <c r="AM15" t="n">
+      <c r="AV15" t="n">
         <v>495.06</v>
       </c>
-      <c r="AN15" t="n">
+      <c r="AW15" t="n">
         <v>495.0833333333333</v>
       </c>
-      <c r="AO15" t="n">
+      <c r="AX15" t="n">
         <v>495.2142857142857</v>
       </c>
-      <c r="AP15" t="n">
+      <c r="AY15" t="n">
         <v>495.325</v>
       </c>
-      <c r="AQ15" t="n">
+      <c r="AZ15" t="n">
         <v>495.7944444444444</v>
       </c>
-      <c r="AR15" t="n">
+      <c r="BA15" t="n">
         <v>495.95</v>
       </c>
-      <c r="AS15" t="n">
+      <c r="BB15" t="n">
         <v>69.25241873032306</v>
       </c>
-      <c r="AT15" t="n">
+      <c r="BC15" t="n">
         <v>61.78384362706268</v>
       </c>
-      <c r="AU15" t="n">
+      <c r="BD15" t="n">
         <v>56.83985727462728</v>
       </c>
-      <c r="AV15" t="n">
+      <c r="BE15" t="n">
         <v>53.46247656066824</v>
       </c>
-      <c r="AW15" t="n">
+      <c r="BF15" t="n">
         <v>50.37221180593743</v>
       </c>
-      <c r="AX15" t="n">
+      <c r="BG15" t="n">
         <v>47.91581691053677</v>
       </c>
-      <c r="AY15" t="n">
+      <c r="BH15" t="n">
         <v>45.89029717707219</v>
       </c>
-      <c r="AZ15" t="n">
+      <c r="BI15" t="n">
         <v>44.61249167643797</v>
       </c>
-      <c r="BA15" t="n">
+      <c r="BJ15" t="n">
         <v>43.05481970697357</v>
       </c>
-      <c r="BB15" t="n">
+      <c r="BK15" t="n">
         <v>332</v>
       </c>
-      <c r="BC15" t="n">
+      <c r="BL15" t="n">
         <v>332</v>
       </c>
-      <c r="BD15" t="n">
+      <c r="BM15" t="n">
         <v>332</v>
       </c>
-      <c r="BE15" t="n">
+      <c r="BN15" t="n">
         <v>332</v>
       </c>
-      <c r="BF15" t="n">
+      <c r="BO15" t="n">
         <v>332</v>
       </c>
-      <c r="BG15" t="n">
+      <c r="BP15" t="n">
         <v>332</v>
       </c>
-      <c r="BH15" t="n">
+      <c r="BQ15" t="n">
         <v>332</v>
       </c>
-      <c r="BI15" t="n">
+      <c r="BR15" t="n">
         <v>332</v>
       </c>
-      <c r="BJ15" t="n">
+      <c r="BS15" t="n">
         <v>332</v>
       </c>
-      <c r="BK15" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL15" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM15" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN15" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO15" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP15" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ15" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR15" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS15" t="n">
-        <v>669</v>
-      </c>
       <c r="BT15" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX15" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY15" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ15" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA15" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB15" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC15" t="n">
         <v>0.7</v>
       </c>
-      <c r="BU15" t="n">
+      <c r="CD15" t="n">
         <v>0.4736842105263158</v>
       </c>
-      <c r="BV15" t="n">
+      <c r="CE15" t="n">
         <v>0.5185185185185185</v>
       </c>
-      <c r="BW15" t="n">
+      <c r="CF15" t="n">
         <v>0.5135135135135135</v>
       </c>
-      <c r="BX15" t="n">
+      <c r="CG15" t="n">
         <v>0.4565217391304348</v>
       </c>
-      <c r="BY15" t="n">
+      <c r="CH15" t="n">
         <v>0.4897959183673469</v>
       </c>
-      <c r="BZ15" t="n">
+      <c r="CI15" t="n">
         <v>0.04081632653061224</v>
       </c>
-      <c r="CA15" t="n">
+      <c r="CJ15" t="n">
         <v>0.5714285714285714</v>
       </c>
-      <c r="CB15" t="n">
+      <c r="CK15" t="n">
         <v>0.673469387755102</v>
+      </c>
+      <c r="CL15" t="n">
+        <v>496.37</v>
+      </c>
+      <c r="CM15" t="n">
+        <v>25.02</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S16_G4_500_21_REL2</t>
+          <t>S15_G4_499_20_REL2</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="C16" t="n">
-        <v>21</v>
+        <v>29.65159377316531</v>
       </c>
       <c r="D16" t="n">
-        <v>31.13417346182357</v>
+        <v>20</v>
       </c>
       <c r="E16" t="n">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="F16" t="n">
         <v>200</v>
       </c>
       <c r="G16" t="n">
-        <v>0.535</v>
-      </c>
-      <c r="H16" t="inlineStr">
+        <v>78.5</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="N16" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="O16" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="Q16" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I16" t="n">
-        <v>496.8522625024322</v>
-      </c>
-      <c r="J16" t="n">
-        <v>23.36317535633122</v>
-      </c>
-      <c r="K16" t="n">
-        <v>494.9557386839467</v>
-      </c>
-      <c r="L16" t="n">
-        <v>19.80377968137126</v>
-      </c>
-      <c r="M16" t="n">
-        <v>496.233119016323</v>
-      </c>
-      <c r="N16" t="n">
-        <v>24.32076812150454</v>
-      </c>
-      <c r="O16" t="n">
-        <v>498.4275852630605</v>
-      </c>
-      <c r="P16" t="n">
-        <v>28.87039522892933</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>497.3720531655707</v>
-      </c>
       <c r="R16" t="n">
-        <v>27.45131171241167</v>
+        <v>499.26</v>
       </c>
       <c r="S16" t="n">
-        <v>498.6278939503363</v>
+        <v>21.17</v>
       </c>
       <c r="T16" t="n">
-        <v>26.99473094579147</v>
+        <v>502.69</v>
       </c>
       <c r="U16" t="n">
-        <v>497.0941339192512</v>
+        <v>23.55</v>
       </c>
       <c r="V16" t="n">
-        <v>26.26570983735899</v>
+        <v>496.43</v>
       </c>
       <c r="W16" t="n">
-        <v>497.202983581339</v>
+        <v>25.03</v>
       </c>
       <c r="X16" t="n">
-        <v>25.44687757785531</v>
+        <v>493.1</v>
       </c>
       <c r="Y16" t="n">
-        <v>496.650646675875</v>
+        <v>25.37</v>
       </c>
       <c r="Z16" t="n">
-        <v>24.30818721517153</v>
+        <v>491.57</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>25.65</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>495.6</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>25.24</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>497.73</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>24.62</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>497.01</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>25.41</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>498.79</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>25.64</v>
       </c>
       <c r="AJ16" t="n">
-        <v>499.15</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>497.2833333333334</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
-        <v>497.4375</v>
+        <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>499.24</v>
+        <v>0</v>
       </c>
       <c r="AN16" t="n">
-        <v>500.4666666666666</v>
+        <v>0</v>
       </c>
       <c r="AO16" t="n">
-        <v>501.2357142857143</v>
+        <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>501.90625</v>
+        <v>0</v>
       </c>
       <c r="AQ16" t="n">
-        <v>502.1222222222222</v>
+        <v>0</v>
       </c>
       <c r="AR16" t="n">
-        <v>501.87</v>
+        <v>0</v>
       </c>
       <c r="AS16" t="n">
-        <v>73.68464901185321</v>
+        <v>496.4</v>
       </c>
       <c r="AT16" t="n">
-        <v>61.18771436235291</v>
+        <v>497.9666666666666</v>
       </c>
       <c r="AU16" t="n">
-        <v>54.35366679213096</v>
+        <v>496.5875</v>
       </c>
       <c r="AV16" t="n">
-        <v>50.90896188295338</v>
+        <v>496.06</v>
       </c>
       <c r="AW16" t="n">
-        <v>48.51905696619514</v>
+        <v>495.0583333333333</v>
       </c>
       <c r="AX16" t="n">
-        <v>46.47973609377465</v>
+        <v>494.5928571428572</v>
       </c>
       <c r="AY16" t="n">
-        <v>44.5859839068008</v>
+        <v>495</v>
       </c>
       <c r="AZ16" t="n">
-        <v>42.77377903388366</v>
+        <v>495.7833333333334</v>
       </c>
       <c r="BA16" t="n">
-        <v>41.50051927385969</v>
+        <v>496.305</v>
       </c>
       <c r="BB16" t="n">
-        <v>331</v>
+        <v>66.45592524372827</v>
       </c>
       <c r="BC16" t="n">
-        <v>331</v>
+        <v>56.20764084080464</v>
       </c>
       <c r="BD16" t="n">
-        <v>331</v>
+        <v>51.25346177332806</v>
       </c>
       <c r="BE16" t="n">
-        <v>331</v>
+        <v>47.39700834440924</v>
       </c>
       <c r="BF16" t="n">
-        <v>331</v>
+        <v>44.90365535108349</v>
       </c>
       <c r="BG16" t="n">
-        <v>331</v>
+        <v>42.82654324274198</v>
       </c>
       <c r="BH16" t="n">
-        <v>331</v>
+        <v>41.10109487592757</v>
       </c>
       <c r="BI16" t="n">
-        <v>331</v>
+        <v>39.38094223239347</v>
       </c>
       <c r="BJ16" t="n">
-        <v>331</v>
+        <v>38.38413702299428</v>
       </c>
       <c r="BK16" t="n">
-        <v>669</v>
+        <v>341</v>
       </c>
       <c r="BL16" t="n">
-        <v>669</v>
+        <v>341</v>
       </c>
       <c r="BM16" t="n">
-        <v>669</v>
+        <v>341</v>
       </c>
       <c r="BN16" t="n">
-        <v>669</v>
+        <v>341</v>
       </c>
       <c r="BO16" t="n">
-        <v>669</v>
+        <v>341</v>
       </c>
       <c r="BP16" t="n">
-        <v>669</v>
+        <v>341</v>
       </c>
       <c r="BQ16" t="n">
-        <v>669</v>
+        <v>341</v>
       </c>
       <c r="BR16" t="n">
-        <v>669</v>
+        <v>341</v>
       </c>
       <c r="BS16" t="n">
-        <v>669</v>
+        <v>341</v>
       </c>
       <c r="BT16" t="n">
-        <v>0</v>
+        <v>669</v>
       </c>
       <c r="BU16" t="n">
-        <v>0</v>
+        <v>669</v>
       </c>
       <c r="BV16" t="n">
-        <v>0</v>
+        <v>669</v>
       </c>
       <c r="BW16" t="n">
-        <v>0.7</v>
+        <v>669</v>
       </c>
       <c r="BX16" t="n">
-        <v>0.6923076923076923</v>
+        <v>669</v>
       </c>
       <c r="BY16" t="n">
-        <v>0.6764705882352942</v>
+        <v>669</v>
       </c>
       <c r="BZ16" t="n">
-        <v>0.7435897435897436</v>
+        <v>669</v>
       </c>
       <c r="CA16" t="n">
-        <v>0.7209302325581395</v>
+        <v>669</v>
       </c>
       <c r="CB16" t="n">
-        <v>0.6470588235294118</v>
+        <v>669</v>
+      </c>
+      <c r="CC16" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD16" t="n">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="CE16" t="n">
+        <v>0.7391304347826086</v>
+      </c>
+      <c r="CF16" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="CG16" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="CH16" t="n">
+        <v>0.9459459459459459</v>
+      </c>
+      <c r="CI16" t="n">
+        <v>0.975609756097561</v>
+      </c>
+      <c r="CJ16" t="n">
+        <v>0.8723404255319149</v>
+      </c>
+      <c r="CK16" t="n">
+        <v>0.8367346938775511</v>
+      </c>
+      <c r="CL16" t="n">
+        <v>498.79</v>
+      </c>
+      <c r="CM16" t="n">
+        <v>25.64</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S15_G4_499_20_REL2</t>
+          <t>S16_G4_500_21_REL2</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C17" t="n">
-        <v>20</v>
+        <v>31.13417346182357</v>
       </c>
       <c r="D17" t="n">
-        <v>29.65159377316531</v>
+        <v>21</v>
       </c>
       <c r="E17" t="n">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="F17" t="n">
         <v>200</v>
       </c>
       <c r="G17" t="n">
-        <v>0.485</v>
-      </c>
-      <c r="H17" t="inlineStr">
+        <v>79.5</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="L17" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="M17" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="N17" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="O17" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="Q17" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I17" t="n">
-        <v>499.2604780435099</v>
-      </c>
-      <c r="J17" t="n">
-        <v>21.17380218166086</v>
-      </c>
-      <c r="K17" t="n">
-        <v>502.692955490215</v>
-      </c>
-      <c r="L17" t="n">
-        <v>23.54733453112292</v>
-      </c>
-      <c r="M17" t="n">
-        <v>496.4314119246532</v>
-      </c>
-      <c r="N17" t="n">
-        <v>25.02788322726562</v>
-      </c>
-      <c r="O17" t="n">
-        <v>493.0999377698668</v>
-      </c>
-      <c r="P17" t="n">
-        <v>25.37451352103487</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>491.573453074251</v>
-      </c>
       <c r="R17" t="n">
-        <v>25.65120801122317</v>
+        <v>496.85</v>
       </c>
       <c r="S17" t="n">
-        <v>495.6033270490431</v>
+        <v>23.36</v>
       </c>
       <c r="T17" t="n">
-        <v>25.23656319435218</v>
+        <v>494.96</v>
       </c>
       <c r="U17" t="n">
-        <v>497.73404879045</v>
+        <v>19.8</v>
       </c>
       <c r="V17" t="n">
-        <v>24.62391119564688</v>
+        <v>496.23</v>
       </c>
       <c r="W17" t="n">
-        <v>497.0081391089972</v>
+        <v>24.32</v>
       </c>
       <c r="X17" t="n">
-        <v>25.40625152076669</v>
+        <v>498.43</v>
       </c>
       <c r="Y17" t="n">
-        <v>498.7851278048477</v>
+        <v>28.87</v>
       </c>
       <c r="Z17" t="n">
-        <v>25.64355311238556</v>
+        <v>497.37</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>27.45</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>498.63</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>26.99</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>497.09</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>26.27</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>497.2</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>25.45</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>496.65</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>24.31</v>
       </c>
       <c r="AJ17" t="n">
-        <v>496.4</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>497.9666666666666</v>
+        <v>0</v>
       </c>
       <c r="AL17" t="n">
-        <v>496.5875</v>
+        <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>496.06</v>
+        <v>0</v>
       </c>
       <c r="AN17" t="n">
-        <v>495.0583333333333</v>
+        <v>0</v>
       </c>
       <c r="AO17" t="n">
-        <v>494.5928571428572</v>
+        <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>495</v>
+        <v>0</v>
       </c>
       <c r="AQ17" t="n">
-        <v>495.7833333333334</v>
+        <v>0</v>
       </c>
       <c r="AR17" t="n">
-        <v>496.305</v>
+        <v>0</v>
       </c>
       <c r="AS17" t="n">
-        <v>66.45592524372827</v>
+        <v>499.15</v>
       </c>
       <c r="AT17" t="n">
-        <v>56.20764084080464</v>
+        <v>497.2833333333334</v>
       </c>
       <c r="AU17" t="n">
-        <v>51.25346177332806</v>
+        <v>497.4375</v>
       </c>
       <c r="AV17" t="n">
-        <v>47.39700834440924</v>
+        <v>499.24</v>
       </c>
       <c r="AW17" t="n">
-        <v>44.90365535108349</v>
+        <v>500.4666666666666</v>
       </c>
       <c r="AX17" t="n">
-        <v>42.82654324274198</v>
+        <v>501.2357142857143</v>
       </c>
       <c r="AY17" t="n">
-        <v>41.10109487592757</v>
+        <v>501.90625</v>
       </c>
       <c r="AZ17" t="n">
-        <v>39.38094223239347</v>
+        <v>502.1222222222222</v>
       </c>
       <c r="BA17" t="n">
-        <v>38.38413702299428</v>
+        <v>501.87</v>
       </c>
       <c r="BB17" t="n">
-        <v>341</v>
+        <v>73.68464901185321</v>
       </c>
       <c r="BC17" t="n">
-        <v>341</v>
+        <v>61.18771436235291</v>
       </c>
       <c r="BD17" t="n">
-        <v>341</v>
+        <v>54.35366679213096</v>
       </c>
       <c r="BE17" t="n">
-        <v>341</v>
+        <v>50.90896188295338</v>
       </c>
       <c r="BF17" t="n">
-        <v>341</v>
+        <v>48.51905696619514</v>
       </c>
       <c r="BG17" t="n">
-        <v>341</v>
+        <v>46.47973609377465</v>
       </c>
       <c r="BH17" t="n">
-        <v>341</v>
+        <v>44.5859839068008</v>
       </c>
       <c r="BI17" t="n">
-        <v>341</v>
+        <v>42.77377903388366</v>
       </c>
       <c r="BJ17" t="n">
-        <v>341</v>
+        <v>41.50051927385969</v>
       </c>
       <c r="BK17" t="n">
-        <v>669</v>
+        <v>331</v>
       </c>
       <c r="BL17" t="n">
-        <v>669</v>
+        <v>331</v>
       </c>
       <c r="BM17" t="n">
-        <v>669</v>
+        <v>331</v>
       </c>
       <c r="BN17" t="n">
-        <v>669</v>
+        <v>331</v>
       </c>
       <c r="BO17" t="n">
-        <v>669</v>
+        <v>331</v>
       </c>
       <c r="BP17" t="n">
-        <v>669</v>
+        <v>331</v>
       </c>
       <c r="BQ17" t="n">
-        <v>669</v>
+        <v>331</v>
       </c>
       <c r="BR17" t="n">
-        <v>669</v>
+        <v>331</v>
       </c>
       <c r="BS17" t="n">
-        <v>669</v>
+        <v>331</v>
       </c>
       <c r="BT17" t="n">
-        <v>1</v>
+        <v>669</v>
       </c>
       <c r="BU17" t="n">
-        <v>0.7142857142857143</v>
+        <v>669</v>
       </c>
       <c r="BV17" t="n">
-        <v>0.7391304347826086</v>
+        <v>669</v>
       </c>
       <c r="BW17" t="n">
-        <v>0.96</v>
+        <v>669</v>
       </c>
       <c r="BX17" t="n">
-        <v>0.9</v>
+        <v>669</v>
       </c>
       <c r="BY17" t="n">
-        <v>0.9459459459459459</v>
+        <v>669</v>
       </c>
       <c r="BZ17" t="n">
-        <v>0.975609756097561</v>
+        <v>669</v>
       </c>
       <c r="CA17" t="n">
-        <v>0.8723404255319149</v>
+        <v>669</v>
       </c>
       <c r="CB17" t="n">
-        <v>0.8367346938775511</v>
+        <v>669</v>
+      </c>
+      <c r="CC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF17" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="CG17" t="n">
+        <v>0.6923076923076923</v>
+      </c>
+      <c r="CH17" t="n">
+        <v>0.6764705882352942</v>
+      </c>
+      <c r="CI17" t="n">
+        <v>0.7435897435897436</v>
+      </c>
+      <c r="CJ17" t="n">
+        <v>0.7209302325581395</v>
+      </c>
+      <c r="CK17" t="n">
+        <v>0.6470588235294118</v>
+      </c>
+      <c r="CL17" t="n">
+        <v>496.65</v>
+      </c>
+      <c r="CM17" t="n">
+        <v>24.31</v>
       </c>
     </row>
     <row r="18">
@@ -4776,10 +5359,10 @@
         <v>502</v>
       </c>
       <c r="C18" t="n">
+        <v>28.16901408450704</v>
+      </c>
+      <c r="D18" t="n">
         <v>19</v>
-      </c>
-      <c r="D18" t="n">
-        <v>28.16901408450704</v>
       </c>
       <c r="E18" t="n">
         <v>502</v>
@@ -4788,228 +5371,261 @@
         <v>200</v>
       </c>
       <c r="G18" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H18" t="inlineStr">
+        <v>81</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="L18" t="n">
+        <v>2</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="N18" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="O18" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="Q18" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I18" t="n">
-        <v>496.2448444810688</v>
-      </c>
-      <c r="J18" t="n">
-        <v>13.72669622130482</v>
-      </c>
-      <c r="K18" t="n">
-        <v>502.1349545534705</v>
-      </c>
-      <c r="L18" t="n">
-        <v>26.84496850857452</v>
-      </c>
-      <c r="M18" t="n">
-        <v>497.6817418847073</v>
-      </c>
-      <c r="N18" t="n">
-        <v>23.53634253154172</v>
-      </c>
-      <c r="O18" t="n">
-        <v>500.2410628135709</v>
-      </c>
-      <c r="P18" t="n">
-        <v>23.05528623625006</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>498.8932835780778</v>
-      </c>
       <c r="R18" t="n">
-        <v>21.77181011948464</v>
+        <v>496.24</v>
       </c>
       <c r="S18" t="n">
-        <v>498.8968005434209</v>
+        <v>13.73</v>
       </c>
       <c r="T18" t="n">
-        <v>20.42395088952524</v>
+        <v>502.13</v>
       </c>
       <c r="U18" t="n">
-        <v>499.9079115957344</v>
+        <v>26.84</v>
       </c>
       <c r="V18" t="n">
-        <v>21.23711071199402</v>
+        <v>497.68</v>
       </c>
       <c r="W18" t="n">
-        <v>499.2276004754009</v>
+        <v>23.54</v>
       </c>
       <c r="X18" t="n">
-        <v>20.4322843355406</v>
+        <v>500.24</v>
       </c>
       <c r="Y18" t="n">
-        <v>499.4699269564542</v>
+        <v>23.06</v>
       </c>
       <c r="Z18" t="n">
-        <v>20.31563517172191</v>
+        <v>498.89</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>21.77</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>498.9</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>20.42</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>499.91</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>21.24</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>499.23</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>20.43</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>499.47</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>20.32</v>
       </c>
       <c r="AJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS18" t="n">
         <v>501.6</v>
       </c>
-      <c r="AK18" t="n">
+      <c r="AT18" t="n">
         <v>500.3666666666667</v>
       </c>
-      <c r="AL18" t="n">
+      <c r="AU18" t="n">
         <v>499.8125</v>
       </c>
-      <c r="AM18" t="n">
+      <c r="AV18" t="n">
         <v>499.15</v>
       </c>
-      <c r="AN18" t="n">
+      <c r="AW18" t="n">
         <v>498.95</v>
       </c>
-      <c r="AO18" t="n">
+      <c r="AX18" t="n">
         <v>498.8428571428572</v>
       </c>
-      <c r="AP18" t="n">
+      <c r="AY18" t="n">
         <v>498.9625</v>
       </c>
-      <c r="AQ18" t="n">
+      <c r="AZ18" t="n">
         <v>498.9444444444445</v>
       </c>
-      <c r="AR18" t="n">
+      <c r="BA18" t="n">
         <v>499.1</v>
       </c>
-      <c r="AS18" t="n">
+      <c r="BB18" t="n">
         <v>63.52235826856556</v>
       </c>
-      <c r="AT18" t="n">
+      <c r="BC18" t="n">
         <v>55.11744027276868</v>
       </c>
-      <c r="AU18" t="n">
+      <c r="BD18" t="n">
         <v>50.0494989360533</v>
       </c>
-      <c r="AV18" t="n">
+      <c r="BE18" t="n">
         <v>46.2409720918581</v>
       </c>
-      <c r="AW18" t="n">
+      <c r="BF18" t="n">
         <v>43.4869424846892</v>
       </c>
-      <c r="AX18" t="n">
+      <c r="BG18" t="n">
         <v>41.11782224440454</v>
       </c>
-      <c r="AY18" t="n">
+      <c r="BH18" t="n">
         <v>39.37446626622385</v>
       </c>
-      <c r="AZ18" t="n">
+      <c r="BI18" t="n">
         <v>37.92664296920544</v>
       </c>
-      <c r="BA18" t="n">
+      <c r="BJ18" t="n">
         <v>36.38612372869635</v>
       </c>
-      <c r="BB18" t="n">
+      <c r="BK18" t="n">
         <v>338</v>
       </c>
-      <c r="BC18" t="n">
+      <c r="BL18" t="n">
         <v>338</v>
       </c>
-      <c r="BD18" t="n">
+      <c r="BM18" t="n">
         <v>338</v>
       </c>
-      <c r="BE18" t="n">
+      <c r="BN18" t="n">
         <v>338</v>
       </c>
-      <c r="BF18" t="n">
+      <c r="BO18" t="n">
         <v>338</v>
       </c>
-      <c r="BG18" t="n">
+      <c r="BP18" t="n">
         <v>338</v>
       </c>
-      <c r="BH18" t="n">
+      <c r="BQ18" t="n">
         <v>338</v>
       </c>
-      <c r="BI18" t="n">
+      <c r="BR18" t="n">
         <v>338</v>
       </c>
-      <c r="BJ18" t="n">
+      <c r="BS18" t="n">
         <v>338</v>
       </c>
-      <c r="BK18" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL18" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM18" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN18" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO18" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP18" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ18" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR18" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS18" t="n">
-        <v>669</v>
-      </c>
       <c r="BT18" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU18" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV18" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW18" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX18" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY18" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ18" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA18" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB18" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC18" t="n">
         <v>0.875</v>
       </c>
-      <c r="BU18" t="n">
+      <c r="CD18" t="n">
         <v>1</v>
       </c>
-      <c r="BV18" t="n">
+      <c r="CE18" t="n">
         <v>0.7727272727272727</v>
       </c>
-      <c r="BW18" t="n">
+      <c r="CF18" t="n">
         <v>0.8148148148148148</v>
       </c>
-      <c r="BX18" t="n">
+      <c r="CG18" t="n">
         <v>0.7352941176470589</v>
       </c>
-      <c r="BY18" t="n">
+      <c r="CH18" t="n">
         <v>0.9142857142857143</v>
       </c>
-      <c r="BZ18" t="n">
+      <c r="CI18" t="n">
         <v>0.8571428571428571</v>
       </c>
-      <c r="CA18" t="n">
+      <c r="CJ18" t="n">
         <v>0.8541666666666666</v>
       </c>
-      <c r="CB18" t="n">
+      <c r="CK18" t="n">
         <v>0.9791666666666666</v>
+      </c>
+      <c r="CL18" t="n">
+        <v>499.47</v>
+      </c>
+      <c r="CM18" t="n">
+        <v>20.32</v>
       </c>
     </row>
     <row r="19">
@@ -5022,10 +5638,10 @@
         <v>499</v>
       </c>
       <c r="C19" t="n">
+        <v>29.65159377316531</v>
+      </c>
+      <c r="D19" t="n">
         <v>20</v>
-      </c>
-      <c r="D19" t="n">
-        <v>29.65159377316531</v>
       </c>
       <c r="E19" t="n">
         <v>499</v>
@@ -5034,228 +5650,261 @@
         <v>200</v>
       </c>
       <c r="G19" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="H19" t="inlineStr">
+        <v>80</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="M19" t="n">
+        <v>2</v>
+      </c>
+      <c r="N19" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="O19" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="Q19" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I19" t="n">
-        <v>504.6581061424719</v>
-      </c>
-      <c r="J19" t="n">
-        <v>15.25434119085063</v>
-      </c>
-      <c r="K19" t="n">
-        <v>499.5981666440663</v>
-      </c>
-      <c r="L19" t="n">
-        <v>20.99429153187987</v>
-      </c>
-      <c r="M19" t="n">
-        <v>501.6074780003199</v>
-      </c>
-      <c r="N19" t="n">
-        <v>17.73204230311169</v>
-      </c>
-      <c r="O19" t="n">
-        <v>501.685463179113</v>
-      </c>
-      <c r="P19" t="n">
-        <v>20.63035351482419</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>498.8503915575635</v>
-      </c>
       <c r="R19" t="n">
-        <v>19.82224613853361</v>
+        <v>504.66</v>
       </c>
       <c r="S19" t="n">
-        <v>499.0555179246421</v>
+        <v>15.25</v>
       </c>
       <c r="T19" t="n">
-        <v>19.12367656703545</v>
+        <v>499.6</v>
       </c>
       <c r="U19" t="n">
-        <v>499.2245213374273</v>
+        <v>20.99</v>
       </c>
       <c r="V19" t="n">
-        <v>18.77000762774059</v>
+        <v>501.61</v>
       </c>
       <c r="W19" t="n">
-        <v>498.6154611131781</v>
+        <v>17.73</v>
       </c>
       <c r="X19" t="n">
-        <v>18.9781177678622</v>
+        <v>501.69</v>
       </c>
       <c r="Y19" t="n">
-        <v>498.4472156673796</v>
+        <v>20.63</v>
       </c>
       <c r="Z19" t="n">
-        <v>21.06200111527952</v>
+        <v>498.85</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>19.82</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>499.06</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>19.12</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>499.22</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>18.77</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>498.62</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>18.98</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>498.45</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>21.06</v>
       </c>
       <c r="AJ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS19" t="n">
         <v>500.85</v>
       </c>
-      <c r="AK19" t="n">
+      <c r="AT19" t="n">
         <v>501.1666666666667</v>
       </c>
-      <c r="AL19" t="n">
+      <c r="AU19" t="n">
         <v>501.0625</v>
       </c>
-      <c r="AM19" t="n">
+      <c r="AV19" t="n">
         <v>501.34</v>
       </c>
-      <c r="AN19" t="n">
+      <c r="AW19" t="n">
         <v>500.6083333333333</v>
       </c>
-      <c r="AO19" t="n">
+      <c r="AX19" t="n">
         <v>499.6428571428572</v>
       </c>
-      <c r="AP19" t="n">
+      <c r="AY19" t="n">
         <v>499.49375</v>
       </c>
-      <c r="AQ19" t="n">
+      <c r="AZ19" t="n">
         <v>499.4444444444445</v>
       </c>
-      <c r="AR19" t="n">
+      <c r="BA19" t="n">
         <v>499.32</v>
       </c>
-      <c r="AS19" t="n">
+      <c r="BB19" t="n">
         <v>65.7345228932256</v>
       </c>
-      <c r="AT19" t="n">
+      <c r="BC19" t="n">
         <v>55.34804021422579</v>
       </c>
-      <c r="AU19" t="n">
+      <c r="BD19" t="n">
         <v>49.56116013321319</v>
       </c>
-      <c r="AV19" t="n">
+      <c r="BE19" t="n">
         <v>45.85939816438938</v>
       </c>
-      <c r="AW19" t="n">
+      <c r="BF19" t="n">
         <v>43.12854735812721</v>
       </c>
-      <c r="AX19" t="n">
+      <c r="BG19" t="n">
         <v>41.42188369665957</v>
       </c>
-      <c r="AY19" t="n">
+      <c r="BH19" t="n">
         <v>39.52135449269799</v>
       </c>
-      <c r="AZ19" t="n">
+      <c r="BI19" t="n">
         <v>37.78303884934824</v>
       </c>
-      <c r="BA19" t="n">
+      <c r="BJ19" t="n">
         <v>37.00820989996679</v>
       </c>
-      <c r="BB19" t="n">
+      <c r="BK19" t="n">
         <v>326</v>
       </c>
-      <c r="BC19" t="n">
+      <c r="BL19" t="n">
         <v>326</v>
       </c>
-      <c r="BD19" t="n">
+      <c r="BM19" t="n">
         <v>326</v>
       </c>
-      <c r="BE19" t="n">
+      <c r="BN19" t="n">
         <v>326</v>
       </c>
-      <c r="BF19" t="n">
+      <c r="BO19" t="n">
         <v>326</v>
       </c>
-      <c r="BG19" t="n">
+      <c r="BP19" t="n">
         <v>326</v>
       </c>
-      <c r="BH19" t="n">
+      <c r="BQ19" t="n">
         <v>326</v>
       </c>
-      <c r="BI19" t="n">
+      <c r="BR19" t="n">
         <v>326</v>
       </c>
-      <c r="BJ19" t="n">
+      <c r="BS19" t="n">
         <v>326</v>
       </c>
-      <c r="BK19" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL19" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM19" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN19" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO19" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP19" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ19" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR19" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS19" t="n">
-        <v>669</v>
-      </c>
       <c r="BT19" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU19" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV19" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW19" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX19" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY19" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ19" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA19" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB19" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC19" t="n">
         <v>0.875</v>
       </c>
-      <c r="BU19" t="n">
+      <c r="CD19" t="n">
         <v>0.6111111111111112</v>
       </c>
-      <c r="BV19" t="n">
+      <c r="CE19" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="BW19" t="n">
+      <c r="CF19" t="n">
         <v>0.7878787878787878</v>
       </c>
-      <c r="BX19" t="n">
+      <c r="CG19" t="n">
         <v>0.875</v>
       </c>
-      <c r="BY19" t="n">
+      <c r="CH19" t="n">
         <v>0.9512195121951219</v>
       </c>
-      <c r="BZ19" t="n">
+      <c r="CI19" t="n">
         <v>1</v>
       </c>
-      <c r="CA19" t="n">
+      <c r="CJ19" t="n">
         <v>0.9318181818181818</v>
       </c>
-      <c r="CB19" t="n">
+      <c r="CK19" t="n">
         <v>0.8541666666666666</v>
+      </c>
+      <c r="CL19" t="n">
+        <v>498.45</v>
+      </c>
+      <c r="CM19" t="n">
+        <v>21.06</v>
       </c>
     </row>
     <row r="20">
@@ -5268,10 +5917,10 @@
         <v>500</v>
       </c>
       <c r="C20" t="n">
+        <v>26.68643439584878</v>
+      </c>
+      <c r="D20" t="n">
         <v>18</v>
-      </c>
-      <c r="D20" t="n">
-        <v>26.68643439584878</v>
       </c>
       <c r="E20" t="n">
         <v>500</v>
@@ -5280,228 +5929,261 @@
         <v>200</v>
       </c>
       <c r="G20" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="H20" t="inlineStr">
+        <v>81</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="L20" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="M20" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="N20" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="O20" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="Q20" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I20" t="n">
-        <v>508.0939616282624</v>
-      </c>
-      <c r="J20" t="n">
-        <v>27.49751559517556</v>
-      </c>
-      <c r="K20" t="n">
-        <v>500.4754488723061</v>
-      </c>
-      <c r="L20" t="n">
-        <v>28.24351700860599</v>
-      </c>
-      <c r="M20" t="n">
-        <v>497.7154557935202</v>
-      </c>
-      <c r="N20" t="n">
-        <v>26.68285884619001</v>
-      </c>
-      <c r="O20" t="n">
-        <v>498.9856165182968</v>
-      </c>
-      <c r="P20" t="n">
-        <v>24.04168498988791</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>496.3397720457903</v>
-      </c>
       <c r="R20" t="n">
-        <v>23.95267192073571</v>
+        <v>508.09</v>
       </c>
       <c r="S20" t="n">
-        <v>500.4336211975458</v>
+        <v>27.5</v>
       </c>
       <c r="T20" t="n">
-        <v>23.4355071775762</v>
+        <v>500.48</v>
       </c>
       <c r="U20" t="n">
-        <v>500.2873820075683</v>
+        <v>28.24</v>
       </c>
       <c r="V20" t="n">
-        <v>23.16792688289474</v>
+        <v>497.72</v>
       </c>
       <c r="W20" t="n">
-        <v>500.3240982958815</v>
+        <v>26.68</v>
       </c>
       <c r="X20" t="n">
-        <v>23.35344710817786</v>
+        <v>498.99</v>
       </c>
       <c r="Y20" t="n">
-        <v>499.6401485274891</v>
+        <v>24.04</v>
       </c>
       <c r="Z20" t="n">
-        <v>22.72806407258102</v>
+        <v>496.34</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>23.95</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>500.43</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>23.44</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>500.29</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>23.17</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>500.32</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>23.35</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>499.64</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>22.73</v>
       </c>
       <c r="AJ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS20" t="n">
         <v>503.25</v>
       </c>
-      <c r="AK20" t="n">
+      <c r="AT20" t="n">
         <v>505.3833333333333</v>
       </c>
-      <c r="AL20" t="n">
+      <c r="AU20" t="n">
         <v>504.8625</v>
       </c>
-      <c r="AM20" t="n">
+      <c r="AV20" t="n">
         <v>504.34</v>
       </c>
-      <c r="AN20" t="n">
+      <c r="AW20" t="n">
         <v>503.0583333333333</v>
       </c>
-      <c r="AO20" t="n">
+      <c r="AX20" t="n">
         <v>502.3785714285714</v>
       </c>
-      <c r="AP20" t="n">
+      <c r="AY20" t="n">
         <v>501.9375</v>
       </c>
-      <c r="AQ20" t="n">
+      <c r="AZ20" t="n">
         <v>501.6722222222222</v>
       </c>
-      <c r="AR20" t="n">
+      <c r="BA20" t="n">
         <v>500.865</v>
       </c>
-      <c r="AS20" t="n">
+      <c r="BB20" t="n">
         <v>68.23516322249108</v>
       </c>
-      <c r="AT20" t="n">
+      <c r="BC20" t="n">
         <v>58.82660726424925</v>
       </c>
-      <c r="AU20" t="n">
+      <c r="BD20" t="n">
         <v>53.01880415239484</v>
       </c>
-      <c r="AV20" t="n">
+      <c r="BE20" t="n">
         <v>48.6006625469242</v>
       </c>
-      <c r="AW20" t="n">
+      <c r="BF20" t="n">
         <v>45.79215650329456</v>
       </c>
-      <c r="AX20" t="n">
+      <c r="BG20" t="n">
         <v>43.63656197291815</v>
       </c>
-      <c r="AY20" t="n">
+      <c r="BH20" t="n">
         <v>41.82115007684509</v>
       </c>
-      <c r="AZ20" t="n">
+      <c r="BI20" t="n">
         <v>40.5081378045827</v>
       </c>
-      <c r="BA20" t="n">
+      <c r="BJ20" t="n">
         <v>39.19077410564889</v>
       </c>
-      <c r="BB20" t="n">
+      <c r="BK20" t="n">
         <v>334</v>
       </c>
-      <c r="BC20" t="n">
+      <c r="BL20" t="n">
         <v>334</v>
       </c>
-      <c r="BD20" t="n">
+      <c r="BM20" t="n">
         <v>334</v>
       </c>
-      <c r="BE20" t="n">
+      <c r="BN20" t="n">
         <v>334</v>
       </c>
-      <c r="BF20" t="n">
+      <c r="BO20" t="n">
         <v>334</v>
       </c>
-      <c r="BG20" t="n">
+      <c r="BP20" t="n">
         <v>334</v>
       </c>
-      <c r="BH20" t="n">
+      <c r="BQ20" t="n">
         <v>334</v>
       </c>
-      <c r="BI20" t="n">
+      <c r="BR20" t="n">
         <v>334</v>
       </c>
-      <c r="BJ20" t="n">
+      <c r="BS20" t="n">
         <v>334</v>
       </c>
-      <c r="BK20" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL20" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM20" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN20" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO20" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP20" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ20" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR20" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS20" t="n">
-        <v>669</v>
-      </c>
       <c r="BT20" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU20" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV20" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW20" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX20" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY20" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ20" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA20" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB20" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC20" t="n">
         <v>1</v>
       </c>
-      <c r="BU20" t="n">
+      <c r="CD20" t="n">
         <v>1</v>
       </c>
-      <c r="BV20" t="n">
+      <c r="CE20" t="n">
         <v>1</v>
       </c>
-      <c r="BW20" t="n">
+      <c r="CF20" t="n">
         <v>0.9230769230769231</v>
       </c>
-      <c r="BX20" t="n">
+      <c r="CG20" t="n">
         <v>0.967741935483871</v>
       </c>
-      <c r="BY20" t="n">
+      <c r="CH20" t="n">
         <v>0.9743589743589743</v>
       </c>
-      <c r="BZ20" t="n">
+      <c r="CI20" t="n">
         <v>0.9375</v>
       </c>
-      <c r="CA20" t="n">
+      <c r="CJ20" t="n">
         <v>0.8620689655172413</v>
       </c>
-      <c r="CB20" t="n">
+      <c r="CK20" t="n">
         <v>0.9152542372881356</v>
+      </c>
+      <c r="CL20" t="n">
+        <v>499.64</v>
+      </c>
+      <c r="CM20" t="n">
+        <v>22.73</v>
       </c>
     </row>
     <row r="21">
@@ -5514,10 +6196,10 @@
         <v>502</v>
       </c>
       <c r="C21" t="n">
+        <v>32.61675315048184</v>
+      </c>
+      <c r="D21" t="n">
         <v>22</v>
-      </c>
-      <c r="D21" t="n">
-        <v>32.61675315048184</v>
       </c>
       <c r="E21" t="n">
         <v>502</v>
@@ -5526,228 +6208,261 @@
         <v>200</v>
       </c>
       <c r="G21" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="H21" t="inlineStr">
+        <v>81</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="L21" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="M21" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="N21" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="O21" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="Q21" t="inlineStr">
         <is>
           <t>REL2</t>
         </is>
       </c>
-      <c r="I21" t="n">
-        <v>493.8761064943986</v>
-      </c>
-      <c r="J21" t="n">
-        <v>16.79045573141037</v>
-      </c>
-      <c r="K21" t="n">
-        <v>505.1418831474618</v>
-      </c>
-      <c r="L21" t="n">
-        <v>21.49941882908497</v>
-      </c>
-      <c r="M21" t="n">
-        <v>500.9303564802017</v>
-      </c>
-      <c r="N21" t="n">
-        <v>29.52284759119041</v>
-      </c>
-      <c r="O21" t="n">
-        <v>502.2651827783033</v>
-      </c>
-      <c r="P21" t="n">
-        <v>25.63893559013393</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>502.3438259040645</v>
-      </c>
       <c r="R21" t="n">
-        <v>23.54826885347007</v>
+        <v>493.88</v>
       </c>
       <c r="S21" t="n">
-        <v>500.5443078937315</v>
+        <v>16.79</v>
       </c>
       <c r="T21" t="n">
-        <v>23.38856941209579</v>
+        <v>505.14</v>
       </c>
       <c r="U21" t="n">
-        <v>499.4399530309347</v>
+        <v>21.5</v>
       </c>
       <c r="V21" t="n">
-        <v>22.21958352766078</v>
+        <v>500.93</v>
       </c>
       <c r="W21" t="n">
-        <v>499.8389785450776</v>
+        <v>29.52</v>
       </c>
       <c r="X21" t="n">
-        <v>24.32719519659354</v>
+        <v>502.27</v>
       </c>
       <c r="Y21" t="n">
-        <v>496.8069068859037</v>
+        <v>25.64</v>
       </c>
       <c r="Z21" t="n">
-        <v>24.67433811307133</v>
+        <v>502.34</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>23.55</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>500.54</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>23.39</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>499.44</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>22.22</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>499.84</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>24.33</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>496.81</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>24.67</v>
       </c>
       <c r="AJ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS21" t="n">
         <v>494.95</v>
       </c>
-      <c r="AK21" t="n">
+      <c r="AT21" t="n">
         <v>497.65</v>
       </c>
-      <c r="AL21" t="n">
+      <c r="AU21" t="n">
         <v>498.7625</v>
       </c>
-      <c r="AM21" t="n">
+      <c r="AV21" t="n">
         <v>498.96</v>
       </c>
-      <c r="AN21" t="n">
+      <c r="AW21" t="n">
         <v>499.5</v>
       </c>
-      <c r="AO21" t="n">
+      <c r="AX21" t="n">
         <v>499.9</v>
       </c>
-      <c r="AP21" t="n">
+      <c r="AY21" t="n">
         <v>500.475</v>
       </c>
-      <c r="AQ21" t="n">
+      <c r="AZ21" t="n">
         <v>502.3611111111111</v>
       </c>
-      <c r="AR21" t="n">
+      <c r="BA21" t="n">
         <v>503.225</v>
       </c>
-      <c r="AS21" t="n">
+      <c r="BB21" t="n">
         <v>68.11202169955021</v>
       </c>
-      <c r="AT21" t="n">
+      <c r="BC21" t="n">
         <v>57.91857071210696</v>
       </c>
-      <c r="AU21" t="n">
+      <c r="BD21" t="n">
         <v>52.6783266035473</v>
       </c>
-      <c r="AV21" t="n">
+      <c r="BE21" t="n">
         <v>49.58889391789254</v>
       </c>
-      <c r="AW21" t="n">
+      <c r="BF21" t="n">
         <v>46.79458658149822</v>
       </c>
-      <c r="AX21" t="n">
+      <c r="BG21" t="n">
         <v>44.28564746538738</v>
       </c>
-      <c r="AY21" t="n">
+      <c r="BH21" t="n">
         <v>42.23519711094054</v>
       </c>
-      <c r="AZ21" t="n">
+      <c r="BI21" t="n">
         <v>41.68409820554928</v>
       </c>
-      <c r="BA21" t="n">
+      <c r="BJ21" t="n">
         <v>41.00456529461079</v>
       </c>
-      <c r="BB21" t="n">
+      <c r="BK21" t="n">
         <v>322</v>
       </c>
-      <c r="BC21" t="n">
+      <c r="BL21" t="n">
         <v>322</v>
       </c>
-      <c r="BD21" t="n">
+      <c r="BM21" t="n">
         <v>322</v>
       </c>
-      <c r="BE21" t="n">
+      <c r="BN21" t="n">
         <v>322</v>
       </c>
-      <c r="BF21" t="n">
+      <c r="BO21" t="n">
         <v>322</v>
       </c>
-      <c r="BG21" t="n">
+      <c r="BP21" t="n">
         <v>322</v>
       </c>
-      <c r="BH21" t="n">
+      <c r="BQ21" t="n">
         <v>322</v>
       </c>
-      <c r="BI21" t="n">
+      <c r="BR21" t="n">
         <v>322</v>
       </c>
-      <c r="BJ21" t="n">
+      <c r="BS21" t="n">
         <v>322</v>
       </c>
-      <c r="BK21" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL21" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM21" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN21" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO21" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP21" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ21" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR21" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS21" t="n">
-        <v>669</v>
-      </c>
       <c r="BT21" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU21" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV21" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW21" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX21" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY21" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ21" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA21" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB21" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC21" t="n">
         <v>0.9</v>
       </c>
-      <c r="BU21" t="n">
+      <c r="CD21" t="n">
         <v>1</v>
       </c>
-      <c r="BV21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW21" t="n">
+      <c r="CE21" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF21" t="n">
         <v>0.8666666666666667</v>
       </c>
-      <c r="BX21" t="n">
+      <c r="CG21" t="n">
         <v>0.8421052631578947</v>
       </c>
-      <c r="BY21" t="n">
+      <c r="CH21" t="n">
         <v>0.7441860465116279</v>
       </c>
-      <c r="BZ21" t="n">
+      <c r="CI21" t="n">
         <v>0.8181818181818182</v>
       </c>
-      <c r="CA21" t="n">
+      <c r="CJ21" t="n">
         <v>0.8085106382978723</v>
       </c>
-      <c r="CB21" t="n">
+      <c r="CK21" t="n">
         <v>0.7547169811320755</v>
+      </c>
+      <c r="CL21" t="n">
+        <v>496.81</v>
+      </c>
+      <c r="CM21" t="n">
+        <v>24.67</v>
       </c>
     </row>
     <row r="22">
@@ -5760,10 +6475,10 @@
         <v>499.95</v>
       </c>
       <c r="C22" t="n">
+        <v>30.09636767976279</v>
+      </c>
+      <c r="D22" t="n">
         <v>20.3</v>
-      </c>
-      <c r="D22" t="n">
-        <v>30.09636767976279</v>
       </c>
       <c r="E22" t="n">
         <v>499.95</v>
@@ -5772,224 +6487,239 @@
         <v>200</v>
       </c>
       <c r="G22" t="n">
-        <v>0.502</v>
-      </c>
-      <c r="H22" t="inlineStr"/>
+        <v>80.65000000000001</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2.299</v>
+      </c>
       <c r="I22" t="n">
-        <v>499.4141528435179</v>
+        <v>2.222</v>
       </c>
       <c r="J22" t="n">
-        <v>18.25945336363346</v>
+        <v>2.1595</v>
       </c>
       <c r="K22" t="n">
-        <v>500.034192670057</v>
+        <v>2.1185</v>
       </c>
       <c r="L22" t="n">
-        <v>21.28209860926216</v>
+        <v>2.099</v>
       </c>
       <c r="M22" t="n">
-        <v>499.9778555123588</v>
+        <v>2.0935</v>
       </c>
       <c r="N22" t="n">
-        <v>23.03419087204629</v>
+        <v>2.845</v>
       </c>
       <c r="O22" t="n">
-        <v>500.165567302956</v>
+        <v>2.5675</v>
       </c>
       <c r="P22" t="n">
-        <v>23.42801006001252</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>499.34973637077</v>
-      </c>
+        <v>2.3955</v>
+      </c>
+      <c r="Q22" t="inlineStr"/>
       <c r="R22" t="n">
-        <v>22.83412570931787</v>
+        <v>499.4134999999999</v>
       </c>
       <c r="S22" t="n">
-        <v>499.6611533015719</v>
+        <v>18.2595</v>
       </c>
       <c r="T22" t="n">
-        <v>22.56366639979735</v>
+        <v>500.0339999999999</v>
       </c>
       <c r="U22" t="n">
-        <v>499.4340670011567</v>
+        <v>21.282</v>
       </c>
       <c r="V22" t="n">
-        <v>22.7059346812144</v>
+        <v>499.9775000000001</v>
       </c>
       <c r="W22" t="n">
-        <v>499.5523449971574</v>
+        <v>23.0335</v>
       </c>
       <c r="X22" t="n">
-        <v>23.1433877698751</v>
+        <v>500.1665000000001</v>
       </c>
       <c r="Y22" t="n">
-        <v>499.5706742837219</v>
+        <v>23.4275</v>
       </c>
       <c r="Z22" t="n">
-        <v>23.37444244053098</v>
+        <v>499.3495</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>22.834</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>499.6610000000001</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>22.5635</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>499.4335</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>22.7065</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>499.552</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>23.143</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>499.5719999999999</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>23.3745</v>
       </c>
       <c r="AJ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS22" t="n">
         <v>499.0125000000001</v>
       </c>
-      <c r="AK22" t="n">
-        <v>499.3641666666666</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>499.4556249999999</v>
-      </c>
-      <c r="AM22" t="n">
+      <c r="AT22" t="n">
+        <v>499.3645</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>499.456</v>
+      </c>
+      <c r="AV22" t="n">
         <v>499.2655</v>
       </c>
-      <c r="AN22" t="n">
-        <v>499.1075</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>498.9985714285714</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>498.8625</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>499.0275</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>499.09525</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>67.93045296677147</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>57.48731423928369</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>51.59793565319948</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>48.08230798823643</v>
-      </c>
       <c r="AW22" t="n">
-        <v>45.4748406571151</v>
+        <v>499.1085000000001</v>
       </c>
       <c r="AX22" t="n">
-        <v>43.30461050473475</v>
+        <v>498.9984999999999</v>
       </c>
       <c r="AY22" t="n">
-        <v>41.68974389938641</v>
+        <v>498.8615</v>
       </c>
       <c r="AZ22" t="n">
-        <v>40.57720800662258</v>
+        <v>499.0260000000001</v>
       </c>
       <c r="BA22" t="n">
-        <v>39.79552257884441</v>
+        <v>499.0950000000001</v>
       </c>
       <c r="BB22" t="n">
+        <v>67.92949999999999</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>57.4875</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>51.5975</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>48.083</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>45.47499999999999</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>43.30649999999999</v>
+      </c>
+      <c r="BH22" t="n">
+        <v>41.69</v>
+      </c>
+      <c r="BI22" t="n">
+        <v>40.57699999999999</v>
+      </c>
+      <c r="BJ22" t="n">
+        <v>39.79449999999999</v>
+      </c>
+      <c r="BK22" t="n">
         <v>332.5</v>
       </c>
-      <c r="BC22" t="n">
+      <c r="BL22" t="n">
         <v>332.5</v>
       </c>
-      <c r="BD22" t="n">
+      <c r="BM22" t="n">
         <v>332.5</v>
       </c>
-      <c r="BE22" t="n">
+      <c r="BN22" t="n">
         <v>332.5</v>
       </c>
-      <c r="BF22" t="n">
+      <c r="BO22" t="n">
         <v>332.5</v>
       </c>
-      <c r="BG22" t="n">
+      <c r="BP22" t="n">
         <v>332.5</v>
       </c>
-      <c r="BH22" t="n">
+      <c r="BQ22" t="n">
         <v>332.5</v>
       </c>
-      <c r="BI22" t="n">
+      <c r="BR22" t="n">
         <v>332.5</v>
       </c>
-      <c r="BJ22" t="n">
+      <c r="BS22" t="n">
         <v>332.5</v>
       </c>
-      <c r="BK22" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL22" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM22" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN22" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO22" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP22" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ22" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR22" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS22" t="n">
-        <v>669</v>
-      </c>
       <c r="BT22" t="n">
-        <v>0.7050198412698413</v>
+        <v>669</v>
       </c>
       <c r="BU22" t="n">
-        <v>0.6355375240514559</v>
+        <v>669</v>
       </c>
       <c r="BV22" t="n">
-        <v>0.6251271644492469</v>
+        <v>669</v>
       </c>
       <c r="BW22" t="n">
-        <v>0.6909907505072161</v>
+        <v>669</v>
       </c>
       <c r="BX22" t="n">
-        <v>0.5921996338012925</v>
+        <v>669</v>
       </c>
       <c r="BY22" t="n">
-        <v>0.6616650695073963</v>
+        <v>669</v>
       </c>
       <c r="BZ22" t="n">
-        <v>0.6408793218126468</v>
+        <v>669</v>
       </c>
       <c r="CA22" t="n">
-        <v>0.7150959513760551</v>
+        <v>669</v>
       </c>
       <c r="CB22" t="n">
-        <v>0.7176063390626318</v>
+        <v>669</v>
+      </c>
+      <c r="CC22" t="inlineStr"/>
+      <c r="CD22" t="inlineStr"/>
+      <c r="CE22" t="inlineStr"/>
+      <c r="CF22" t="inlineStr"/>
+      <c r="CG22" t="inlineStr"/>
+      <c r="CH22" t="inlineStr"/>
+      <c r="CI22" t="inlineStr"/>
+      <c r="CJ22" t="inlineStr"/>
+      <c r="CK22" t="inlineStr"/>
+      <c r="CL22" t="n">
+        <v>499.5719999999999</v>
+      </c>
+      <c r="CM22" t="n">
+        <v>23.3745</v>
       </c>
     </row>
     <row r="23">
@@ -6002,10 +6732,10 @@
         <v>1.468081454788778</v>
       </c>
       <c r="C23" t="n">
+        <v>1.806199840853158</v>
+      </c>
+      <c r="D23" t="n">
         <v>1.218281792655455</v>
-      </c>
-      <c r="D23" t="n">
-        <v>1.806199840853158</v>
       </c>
       <c r="E23" t="n">
         <v>1.468081454788778</v>
@@ -6014,224 +6744,239 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0.01823819012257984</v>
-      </c>
-      <c r="H23" t="inlineStr"/>
+        <v>1.348488432516786</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.1366093161653256</v>
+      </c>
       <c r="I23" t="n">
-        <v>7.660059170586365</v>
+        <v>0.1522670783784031</v>
       </c>
       <c r="J23" t="n">
-        <v>6.794969802781833</v>
+        <v>0.1473440299363864</v>
       </c>
       <c r="K23" t="n">
-        <v>3.835282491952841</v>
+        <v>0.1418403476114124</v>
       </c>
       <c r="L23" t="n">
-        <v>5.554866524139237</v>
+        <v>0.1397704885649478</v>
       </c>
       <c r="M23" t="n">
-        <v>4.976499376715052</v>
+        <v>0.141580365870413</v>
       </c>
       <c r="N23" t="n">
-        <v>5.423708239601027</v>
+        <v>0.07694837640638665</v>
       </c>
       <c r="O23" t="n">
-        <v>5.23414407991068</v>
+        <v>0.1219091551330873</v>
       </c>
       <c r="P23" t="n">
-        <v>4.299953768079969</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>4.936830643547511</v>
-      </c>
+        <v>0.1441663877900152</v>
+      </c>
+      <c r="Q23" t="inlineStr"/>
       <c r="R23" t="n">
-        <v>3.5498529119039</v>
+        <v>7.66068381927797</v>
       </c>
       <c r="S23" t="n">
-        <v>3.958441079980656</v>
+        <v>6.796003062946554</v>
       </c>
       <c r="T23" t="n">
-        <v>2.858988209745153</v>
+        <v>3.834854557044403</v>
       </c>
       <c r="U23" t="n">
-        <v>3.499698345782336</v>
+        <v>5.553328636715858</v>
       </c>
       <c r="V23" t="n">
-        <v>2.722184754636745</v>
+        <v>4.977628768589996</v>
       </c>
       <c r="W23" t="n">
-        <v>3.481448259993052</v>
+        <v>5.423444501712717</v>
       </c>
       <c r="X23" t="n">
-        <v>2.408178157681558</v>
+        <v>5.234594716127048</v>
       </c>
       <c r="Y23" t="n">
-        <v>3.320887808013457</v>
+        <v>4.299986383087374</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.261095139878781</v>
+        <v>4.937347972343043</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>3.549601015384835</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>3.958580154816271</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>2.858634703564108</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>3.499874095479802</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>2.72198123470851</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>3.481446462849061</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>2.409418143343676</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>3.320246661731149</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>2.261393317590309</v>
       </c>
       <c r="AJ23" t="n">
-        <v>4.492577943558394</v>
+        <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>4.304255595113999</v>
+        <v>0</v>
       </c>
       <c r="AL23" t="n">
-        <v>3.774528279606951</v>
+        <v>0</v>
       </c>
       <c r="AM23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>4.492494178890877</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>4.303229478818015</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>3.773767348419875</v>
+      </c>
+      <c r="AV23" t="n">
         <v>3.783866687036307</v>
       </c>
-      <c r="AN23" t="n">
-        <v>3.940357521553199</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>3.890346227540646</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>3.856412337707297</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>3.69888620777088</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>3.511070640057488</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>2.357364659116608</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>2.305591702279524</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>2.32833951240757</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>2.435030211500682</v>
-      </c>
       <c r="AW23" t="n">
-        <v>2.517945646657871</v>
+        <v>3.941583004193541</v>
       </c>
       <c r="AX23" t="n">
-        <v>2.394811759766788</v>
+        <v>3.891307823720375</v>
       </c>
       <c r="AY23" t="n">
-        <v>2.317672843965907</v>
+        <v>3.856686981553497</v>
       </c>
       <c r="AZ23" t="n">
-        <v>2.205213553020479</v>
+        <v>3.699273612908066</v>
       </c>
       <c r="BA23" t="n">
-        <v>2.246476522230193</v>
+        <v>3.512206533910287</v>
       </c>
       <c r="BB23" t="n">
+        <v>2.356733857202424</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>2.305320790555714</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>2.328098105637666</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>2.434696782158434</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>2.518285757791347</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>2.395197552560012</v>
+      </c>
+      <c r="BH23" t="n">
+        <v>2.317998228962587</v>
+      </c>
+      <c r="BI23" t="n">
+        <v>2.205717689622992</v>
+      </c>
+      <c r="BJ23" t="n">
+        <v>2.245079942311281</v>
+      </c>
+      <c r="BK23" t="n">
         <v>6.61338355951499</v>
       </c>
-      <c r="BC23" t="n">
+      <c r="BL23" t="n">
         <v>6.61338355951499</v>
       </c>
-      <c r="BD23" t="n">
+      <c r="BM23" t="n">
         <v>6.61338355951499</v>
       </c>
-      <c r="BE23" t="n">
+      <c r="BN23" t="n">
         <v>6.61338355951499</v>
       </c>
-      <c r="BF23" t="n">
+      <c r="BO23" t="n">
         <v>6.61338355951499</v>
       </c>
-      <c r="BG23" t="n">
+      <c r="BP23" t="n">
         <v>6.61338355951499</v>
       </c>
-      <c r="BH23" t="n">
+      <c r="BQ23" t="n">
         <v>6.61338355951499</v>
       </c>
-      <c r="BI23" t="n">
+      <c r="BR23" t="n">
         <v>6.61338355951499</v>
       </c>
-      <c r="BJ23" t="n">
+      <c r="BS23" t="n">
         <v>6.61338355951499</v>
       </c>
-      <c r="BK23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS23" t="n">
-        <v>0</v>
-      </c>
       <c r="BT23" t="n">
-        <v>0.3537785303941552</v>
+        <v>0</v>
       </c>
       <c r="BU23" t="n">
-        <v>0.3538423485980285</v>
+        <v>0</v>
       </c>
       <c r="BV23" t="n">
-        <v>0.2988065088189313</v>
+        <v>0</v>
       </c>
       <c r="BW23" t="n">
-        <v>0.2289435304768445</v>
+        <v>0</v>
       </c>
       <c r="BX23" t="n">
-        <v>0.2957120059924638</v>
+        <v>0</v>
       </c>
       <c r="BY23" t="n">
-        <v>0.239805702500326</v>
+        <v>0</v>
       </c>
       <c r="BZ23" t="n">
-        <v>0.3175659447306743</v>
+        <v>0</v>
       </c>
       <c r="CA23" t="n">
-        <v>0.1794625986863726</v>
+        <v>0</v>
       </c>
       <c r="CB23" t="n">
-        <v>0.1627268398369967</v>
+        <v>0</v>
+      </c>
+      <c r="CC23" t="inlineStr"/>
+      <c r="CD23" t="inlineStr"/>
+      <c r="CE23" t="inlineStr"/>
+      <c r="CF23" t="inlineStr"/>
+      <c r="CG23" t="inlineStr"/>
+      <c r="CH23" t="inlineStr"/>
+      <c r="CI23" t="inlineStr"/>
+      <c r="CJ23" t="inlineStr"/>
+      <c r="CK23" t="inlineStr"/>
+      <c r="CL23" t="n">
+        <v>3.320246661731149</v>
+      </c>
+      <c r="CM23" t="n">
+        <v>2.261393317590309</v>
       </c>
     </row>
   </sheetData>
